--- a/src/attributions/attributions_ig_traj_339.xlsx
+++ b/src/attributions/attributions_ig_traj_339.xlsx
@@ -2140,22 +2140,22 @@
         <v>0</v>
       </c>
       <c r="B4" t="n">
-        <v>0.06429307283106987</v>
+        <v>0.1239923216591926</v>
       </c>
       <c r="C4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="D4" t="n">
         <v>0</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.01396702360860627</v>
+        <v>-0.02520701865306864</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.05070646416467148</v>
+        <v>-0.1001089345883473</v>
       </c>
       <c r="G4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="H4" t="n">
         <v>-0</v>
@@ -2164,28 +2164,28 @@
         <v>0</v>
       </c>
       <c r="J4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="K4" t="n">
-        <v>0.0284832630472772</v>
+        <v>0.1255964289685174</v>
       </c>
       <c r="L4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="M4" t="n">
         <v>0</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.00897614281680858</v>
+        <v>-0.02828438917210098</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.04283737863510748</v>
+        <v>-0.06611202529180582</v>
       </c>
       <c r="P4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
         <v>-0</v>
@@ -2194,61 +2194,61 @@
         <v>0</v>
       </c>
       <c r="T4" t="n">
-        <v>4.059303266884753e-12</v>
+        <v>-3.171135843267765e-11</v>
       </c>
       <c r="U4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="V4" t="n">
         <v>0</v>
       </c>
       <c r="W4" t="n">
-        <v>0.002430677062757168</v>
+        <v>0.01600498879009513</v>
       </c>
       <c r="X4" t="n">
-        <v>-0.002264723009229315</v>
+        <v>0.01104402838700288</v>
       </c>
       <c r="Y4" t="n">
         <v>-0</v>
       </c>
       <c r="Z4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AB4" t="n">
         <v>-0</v>
       </c>
       <c r="AC4" t="n">
-        <v>0.009564491815099874</v>
+        <v>-0.05384836807091344</v>
       </c>
       <c r="AD4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AE4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AF4" t="n">
-        <v>0.02489510645042237</v>
+        <v>-0.07975327702806231</v>
       </c>
       <c r="AG4" t="n">
-        <v>0.0003192576355812767</v>
+        <v>-0.07295083473471224</v>
       </c>
       <c r="AH4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AI4" t="n">
         <v>-0</v>
       </c>
       <c r="AJ4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AK4" t="n">
         <v>0</v>
       </c>
       <c r="AL4" t="n">
-        <v>0.01064940423699907</v>
+        <v>0.0122920928170786</v>
       </c>
       <c r="AM4" t="n">
         <v>0</v>
@@ -2257,13 +2257,13 @@
         <v>0</v>
       </c>
       <c r="AO4" t="n">
-        <v>-0.01044222562783347</v>
+        <v>-0.03460017356888957</v>
       </c>
       <c r="AP4" t="n">
-        <v>-0.01496971270438358</v>
+        <v>-0.0387004069409566</v>
       </c>
       <c r="AQ4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AR4" t="n">
         <v>0</v>
@@ -2272,10 +2272,10 @@
         <v>0</v>
       </c>
       <c r="AT4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AU4" t="n">
-        <v>0.07529204721853254</v>
+        <v>0.3614465145572352</v>
       </c>
       <c r="AV4" t="n">
         <v>-0</v>
@@ -2284,79 +2284,79 @@
         <v>0</v>
       </c>
       <c r="AX4" t="n">
-        <v>-0.01623691579784468</v>
+        <v>-0.06349775530659667</v>
       </c>
       <c r="AY4" t="n">
-        <v>-0.06466984156674727</v>
+        <v>-0.06278918046406315</v>
       </c>
       <c r="AZ4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BA4" t="n">
         <v>0</v>
       </c>
       <c r="BB4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BC4" t="n">
         <v>0</v>
       </c>
       <c r="BD4" t="n">
-        <v>0.01296809923460745</v>
+        <v>-0.004218976827276463</v>
       </c>
       <c r="BE4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BF4" t="n">
         <v>0</v>
       </c>
       <c r="BG4" t="n">
-        <v>-0.01071705933840184</v>
+        <v>-0.02718484492738822</v>
       </c>
       <c r="BH4" t="n">
-        <v>-0.003430395332911713</v>
+        <v>-0.009058638624581406</v>
       </c>
       <c r="BI4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BJ4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BK4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BL4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BM4" t="n">
-        <v>0.02482230466933004</v>
+        <v>0.05447898177358751</v>
       </c>
       <c r="BN4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BO4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BP4" t="n">
-        <v>-0.004302850215805456</v>
+        <v>0.08921492924365411</v>
       </c>
       <c r="BQ4" t="n">
-        <v>0.01317836834932395</v>
+        <v>0.08537346400517667</v>
       </c>
       <c r="BR4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BS4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BT4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BU4" t="n">
         <v>-0</v>
       </c>
       <c r="BV4" t="n">
-        <v>0.03875251589265597</v>
+        <v>0.135444003181246</v>
       </c>
       <c r="BW4" t="n">
         <v>0</v>
@@ -2365,148 +2365,148 @@
         <v>0</v>
       </c>
       <c r="BY4" t="n">
-        <v>-0.01511526177341026</v>
+        <v>-0.08508759978917756</v>
       </c>
       <c r="BZ4" t="n">
-        <v>-0.01157814694489413</v>
+        <v>-0.1251405067212328</v>
       </c>
       <c r="CA4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CB4" t="n">
         <v>0</v>
       </c>
       <c r="CC4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CD4" t="n">
         <v>-0</v>
       </c>
       <c r="CE4" t="n">
-        <v>-0.01730644123314177</v>
+        <v>-0.05295637317348042</v>
       </c>
       <c r="CF4" t="n">
         <v>0</v>
       </c>
       <c r="CG4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CH4" t="n">
-        <v>-0.0008444532180280003</v>
+        <v>0.001963548785042206</v>
       </c>
       <c r="CI4" t="n">
-        <v>0.03289684389728131</v>
+        <v>0.08033037196401056</v>
       </c>
       <c r="CJ4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CK4" t="n">
         <v>0</v>
       </c>
       <c r="CL4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CM4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CN4" t="n">
-        <v>0.003036872144909077</v>
+        <v>-0.1417349286295298</v>
       </c>
       <c r="CO4" t="n">
         <v>-0</v>
       </c>
       <c r="CP4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CQ4" t="n">
-        <v>0.008153247475025193</v>
+        <v>0.08497325112304029</v>
       </c>
       <c r="CR4" t="n">
-        <v>-0.005180718479494705</v>
+        <v>0.0621815658409695</v>
       </c>
       <c r="CS4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CT4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CU4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CV4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CW4" t="n">
-        <v>-0.0127499503740992</v>
+        <v>-0.05817398224594496</v>
       </c>
       <c r="CX4" t="n">
         <v>-0</v>
       </c>
       <c r="CY4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CZ4" t="n">
-        <v>-0.003818738890154995</v>
+        <v>-0.008769662880279963</v>
       </c>
       <c r="DA4" t="n">
-        <v>0.03512242978562608</v>
+        <v>0.07409579730192276</v>
       </c>
       <c r="DB4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DC4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DD4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DE4" t="n">
         <v>0</v>
       </c>
       <c r="DF4" t="n">
-        <v>-0.01156298615119952</v>
+        <v>-0.008577675797451277</v>
       </c>
       <c r="DG4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DH4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DI4" t="n">
-        <v>0.0188306440350229</v>
+        <v>-0.06045884397100733</v>
       </c>
       <c r="DJ4" t="n">
-        <v>0.0448282138720263</v>
+        <v>0.003273425442493674</v>
       </c>
       <c r="DK4" t="n">
         <v>0</v>
       </c>
       <c r="DL4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DM4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DN4" t="n">
         <v>-0</v>
       </c>
       <c r="DO4" t="n">
-        <v>-0.01077332771957698</v>
+        <v>-0.0292083614409677</v>
       </c>
       <c r="DP4" t="n">
         <v>0</v>
       </c>
       <c r="DQ4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DR4" t="n">
-        <v>0.01472972816777159</v>
+        <v>0.05437216225584583</v>
       </c>
       <c r="DS4" t="n">
-        <v>0.01102203616677807</v>
+        <v>0.1021531063923696</v>
       </c>
       <c r="DT4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DU4" t="n">
         <v>0</v>
@@ -2518,19 +2518,19 @@
         <v>-0</v>
       </c>
       <c r="DX4" t="n">
-        <v>0.000868179699772218</v>
+        <v>-0.006904452496286765</v>
       </c>
       <c r="DY4" t="n">
         <v>0</v>
       </c>
       <c r="DZ4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EA4" t="n">
-        <v>-0.001958824989677135</v>
+        <v>-0.0001242392384753374</v>
       </c>
       <c r="EB4" t="n">
-        <v>-0.02841742682572978</v>
+        <v>-0.06488692118064446</v>
       </c>
       <c r="EC4" t="n">
         <v>-0</v>
@@ -2542,10 +2542,10 @@
         <v>0</v>
       </c>
       <c r="EF4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EG4" t="n">
-        <v>-0.006070794418332296</v>
+        <v>-0.05640754963005953</v>
       </c>
       <c r="EH4" t="n">
         <v>-0</v>
@@ -2554,52 +2554,52 @@
         <v>0</v>
       </c>
       <c r="EJ4" t="n">
-        <v>-0.00315670930352905</v>
+        <v>-0.04614292964758808</v>
       </c>
       <c r="EK4" t="n">
-        <v>0.0152135397246428</v>
+        <v>0.04314163046083013</v>
       </c>
       <c r="EL4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EM4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EN4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EO4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EP4" t="n">
-        <v>-0.004063714355521829</v>
+        <v>0.01752898657206507</v>
       </c>
       <c r="EQ4" t="n">
         <v>-0</v>
       </c>
       <c r="ER4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ES4" t="n">
-        <v>-0.008277607884733761</v>
+        <v>-0.05477969374329165</v>
       </c>
       <c r="ET4" t="n">
-        <v>0.03344623466272274</v>
+        <v>0.06245749391067699</v>
       </c>
       <c r="EU4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EV4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EW4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EX4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EY4" t="n">
-        <v>-0.01354818353971214</v>
+        <v>-0.06377028054720529</v>
       </c>
       <c r="EZ4" t="n">
         <v>-0</v>
@@ -2608,37 +2608,37 @@
         <v>0</v>
       </c>
       <c r="FB4" t="n">
-        <v>-0.001060460369628185</v>
+        <v>-0.01957675396486989</v>
       </c>
       <c r="FC4" t="n">
-        <v>0.03246483348936476</v>
+        <v>0.06535477012288905</v>
       </c>
       <c r="FD4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FE4" t="n">
         <v>0</v>
       </c>
       <c r="FF4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FG4" t="n">
         <v>0</v>
       </c>
       <c r="FH4" t="n">
-        <v>-0.01516665911036789</v>
+        <v>-0.0993808656730182</v>
       </c>
       <c r="FI4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FJ4" t="n">
         <v>-0</v>
       </c>
       <c r="FK4" t="n">
-        <v>-0.01074221393323599</v>
+        <v>0.01602302582808285</v>
       </c>
       <c r="FL4" t="n">
-        <v>0.0057492451287632</v>
+        <v>-0.03047973646634274</v>
       </c>
       <c r="FM4" t="n">
         <v>0</v>
@@ -2647,25 +2647,25 @@
         <v>-0</v>
       </c>
       <c r="FO4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FP4" t="n">
         <v>-0</v>
       </c>
       <c r="FQ4" t="n">
-        <v>0.000431493949479692</v>
+        <v>0.04534034819324408</v>
       </c>
       <c r="FR4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FS4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FT4" t="n">
-        <v>-0.007034798382076937</v>
+        <v>0.009302500878365904</v>
       </c>
       <c r="FU4" t="n">
-        <v>0.02980008256390167</v>
+        <v>0.06499245206284379</v>
       </c>
       <c r="FV4" t="n">
         <v>-0</v>
@@ -2674,13 +2674,13 @@
         <v>-0</v>
       </c>
       <c r="FX4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FY4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ4" t="n">
-        <v>-0.01825679492905229</v>
+        <v>-0.001933373754376118</v>
       </c>
       <c r="GA4" t="n">
         <v>0</v>
@@ -2689,19 +2689,19 @@
         <v>-0</v>
       </c>
       <c r="GC4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GD4" t="n">
-        <v>-0.008057773556487648</v>
+        <v>0.05329038172126015</v>
       </c>
       <c r="GE4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GF4" t="n">
         <v>0</v>
       </c>
       <c r="GG4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="5">
@@ -2709,43 +2709,43 @@
         <v>-0</v>
       </c>
       <c r="B5" t="n">
-        <v>0.1639105452388937</v>
+        <v>0.2314375498294553</v>
       </c>
       <c r="C5" t="n">
         <v>0</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.04787003325408455</v>
+        <v>-0.09548353771323984</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.05919200675121145</v>
+        <v>-0.04470304160499457</v>
       </c>
       <c r="F5" t="n">
         <v>0</v>
       </c>
       <c r="G5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="H5" t="n">
         <v>-0</v>
       </c>
       <c r="I5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J5" t="n">
         <v>-0</v>
       </c>
       <c r="K5" t="n">
-        <v>0.07358493970379226</v>
+        <v>0.1591947945708778</v>
       </c>
       <c r="L5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.005442499011813508</v>
+        <v>-0.01445104494824487</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.05243867785664008</v>
+        <v>-0.05225051983278638</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -2760,82 +2760,82 @@
         <v>0</v>
       </c>
       <c r="S5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="T5" t="n">
-        <v>0.005588555814666617</v>
+        <v>0.006809519366939147</v>
       </c>
       <c r="U5" t="n">
         <v>-0</v>
       </c>
       <c r="V5" t="n">
-        <v>-0.001307568826308367</v>
+        <v>-0.001423134397429044</v>
       </c>
       <c r="W5" t="n">
-        <v>2.0800651332698e-11</v>
+        <v>4.296025676898227e-13</v>
       </c>
       <c r="X5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Y5" t="n">
         <v>-0</v>
       </c>
       <c r="Z5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA5" t="n">
         <v>0</v>
       </c>
       <c r="AB5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AC5" t="n">
-        <v>0.04082766190257242</v>
+        <v>-0.02682289633663341</v>
       </c>
       <c r="AD5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AE5" t="n">
-        <v>0.01402107418372941</v>
+        <v>-0.06622505412160504</v>
       </c>
       <c r="AF5" t="n">
-        <v>0.05796955295108158</v>
+        <v>-0.0762454692360163</v>
       </c>
       <c r="AG5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AH5" t="n">
         <v>0</v>
       </c>
       <c r="AI5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AJ5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AK5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AL5" t="n">
-        <v>-0.01051618807673014</v>
+        <v>0.09921631014405109</v>
       </c>
       <c r="AM5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AN5" t="n">
-        <v>-0.02676447212143283</v>
+        <v>-0.02492147506867835</v>
       </c>
       <c r="AO5" t="n">
-        <v>-0.05851221543402799</v>
+        <v>0.04321376150673897</v>
       </c>
       <c r="AP5" t="n">
         <v>0</v>
       </c>
       <c r="AQ5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AR5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AS5" t="n">
         <v>0</v>
@@ -2844,25 +2844,25 @@
         <v>-0</v>
       </c>
       <c r="AU5" t="n">
-        <v>0.3239898991410487</v>
+        <v>0.3297100875375366</v>
       </c>
       <c r="AV5" t="n">
         <v>-0</v>
       </c>
       <c r="AW5" t="n">
-        <v>0.02801068832400167</v>
+        <v>-0.1515711179855267</v>
       </c>
       <c r="AX5" t="n">
-        <v>0.1062706334172406</v>
+        <v>-0.1634178543142538</v>
       </c>
       <c r="AY5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AZ5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BA5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BB5" t="n">
         <v>-0</v>
@@ -2871,16 +2871,16 @@
         <v>-0</v>
       </c>
       <c r="BD5" t="n">
-        <v>0.004775735095956275</v>
+        <v>-0.01159397826378499</v>
       </c>
       <c r="BE5" t="n">
         <v>0</v>
       </c>
       <c r="BF5" t="n">
-        <v>-0.03550175095233999</v>
+        <v>-0.003456344711835124</v>
       </c>
       <c r="BG5" t="n">
-        <v>-0.03030491915897163</v>
+        <v>-0.008995175138571095</v>
       </c>
       <c r="BH5" t="n">
         <v>0</v>
@@ -2889,31 +2889,31 @@
         <v>-0</v>
       </c>
       <c r="BJ5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BK5" t="n">
         <v>0</v>
       </c>
       <c r="BL5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BM5" t="n">
-        <v>0.1157765085461797</v>
+        <v>-0.007462284319247737</v>
       </c>
       <c r="BN5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BO5" t="n">
-        <v>0.03692086039894865</v>
+        <v>0.05173103762018494</v>
       </c>
       <c r="BP5" t="n">
-        <v>0.1249795250180095</v>
+        <v>0.07846104706359226</v>
       </c>
       <c r="BQ5" t="n">
         <v>-0</v>
       </c>
       <c r="BR5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BS5" t="n">
         <v>-0</v>
@@ -2925,43 +2925,43 @@
         <v>-0</v>
       </c>
       <c r="BV5" t="n">
-        <v>0.1682607850547932</v>
+        <v>0.2252188008549627</v>
       </c>
       <c r="BW5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BX5" t="n">
-        <v>0.01485419370654943</v>
+        <v>-0.1208822142886236</v>
       </c>
       <c r="BY5" t="n">
-        <v>0.01181702302001457</v>
+        <v>-0.02454017434404576</v>
       </c>
       <c r="BZ5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CA5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CB5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CC5" t="n">
         <v>0</v>
       </c>
       <c r="CD5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CE5" t="n">
-        <v>-0.04604807889380794</v>
+        <v>-0.12668573724677</v>
       </c>
       <c r="CF5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CG5" t="n">
-        <v>0.01382340438780822</v>
+        <v>0.09390088180714395</v>
       </c>
       <c r="CH5" t="n">
-        <v>-0.0003403033130929538</v>
+        <v>0.02606862136427988</v>
       </c>
       <c r="CI5" t="n">
         <v>-0</v>
@@ -2970,7 +2970,7 @@
         <v>-0</v>
       </c>
       <c r="CK5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CL5" t="n">
         <v>-0</v>
@@ -2979,43 +2979,43 @@
         <v>0</v>
       </c>
       <c r="CN5" t="n">
-        <v>-0.04797601658392313</v>
+        <v>-0.105300401754107</v>
       </c>
       <c r="CO5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CP5" t="n">
-        <v>-0.03772570314251643</v>
+        <v>0.08015088722029708</v>
       </c>
       <c r="CQ5" t="n">
-        <v>-0.1293943229333365</v>
+        <v>0.05696125019363391</v>
       </c>
       <c r="CR5" t="n">
         <v>0</v>
       </c>
       <c r="CS5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CT5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CU5" t="n">
         <v>-0</v>
       </c>
       <c r="CV5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CW5" t="n">
-        <v>-0.0360384542851979</v>
+        <v>-0.1337854816437747</v>
       </c>
       <c r="CX5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CY5" t="n">
-        <v>0.02763342636219178</v>
+        <v>0.1092019145019257</v>
       </c>
       <c r="CZ5" t="n">
-        <v>0.01688630941124043</v>
+        <v>0.02941198119192865</v>
       </c>
       <c r="DA5" t="n">
         <v>0</v>
@@ -3033,22 +3033,22 @@
         <v>0</v>
       </c>
       <c r="DF5" t="n">
-        <v>-0.002228109257963446</v>
+        <v>-0.005839244437311599</v>
       </c>
       <c r="DG5" t="n">
         <v>0</v>
       </c>
       <c r="DH5" t="n">
-        <v>0.01609872965103978</v>
+        <v>0.02618236920477075</v>
       </c>
       <c r="DI5" t="n">
-        <v>-0.01981449524947116</v>
+        <v>-0.08956517193576952</v>
       </c>
       <c r="DJ5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DK5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DL5" t="n">
         <v>0</v>
@@ -3060,52 +3060,52 @@
         <v>-0</v>
       </c>
       <c r="DO5" t="n">
-        <v>-0.06960458044200507</v>
+        <v>-0.08006686804391244</v>
       </c>
       <c r="DP5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DQ5" t="n">
-        <v>-0.003440579031213568</v>
+        <v>0.0493626637024212</v>
       </c>
       <c r="DR5" t="n">
-        <v>-0.001007165934400097</v>
+        <v>-0.02772530789976345</v>
       </c>
       <c r="DS5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DT5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DU5" t="n">
         <v>0</v>
       </c>
       <c r="DV5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DW5" t="n">
         <v>-0</v>
       </c>
       <c r="DX5" t="n">
-        <v>0.02100507901067758</v>
+        <v>0.06038288148329</v>
       </c>
       <c r="DY5" t="n">
         <v>0</v>
       </c>
       <c r="DZ5" t="n">
-        <v>-0.04171581193312426</v>
+        <v>0.02732312141678273</v>
       </c>
       <c r="EA5" t="n">
-        <v>-0.03332901492430156</v>
+        <v>-0.02717377344291197</v>
       </c>
       <c r="EB5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EC5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ED5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EE5" t="n">
         <v>-0</v>
@@ -3114,19 +3114,19 @@
         <v>0</v>
       </c>
       <c r="EG5" t="n">
-        <v>-0.03877775721758815</v>
+        <v>-0.07965193467176634</v>
       </c>
       <c r="EH5" t="n">
         <v>-0</v>
       </c>
       <c r="EI5" t="n">
-        <v>0.03934841491841603</v>
+        <v>0.1026051496216689</v>
       </c>
       <c r="EJ5" t="n">
-        <v>0.05573458049432097</v>
+        <v>0.035678073166542</v>
       </c>
       <c r="EK5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EL5" t="n">
         <v>-0</v>
@@ -3141,70 +3141,70 @@
         <v>0</v>
       </c>
       <c r="EP5" t="n">
-        <v>-0.04212301690418252</v>
+        <v>-0.07773759204621034</v>
       </c>
       <c r="EQ5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ER5" t="n">
-        <v>0.03480684543601659</v>
+        <v>0.06728731622601396</v>
       </c>
       <c r="ES5" t="n">
-        <v>-0.01757701770478821</v>
+        <v>-0.01754866889359042</v>
       </c>
       <c r="ET5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EU5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EV5" t="n">
         <v>-0</v>
       </c>
       <c r="EW5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EX5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EY5" t="n">
-        <v>-0.03884492852211018</v>
+        <v>-0.1403117090378536</v>
       </c>
       <c r="EZ5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FA5" t="n">
-        <v>0.02718978323482251</v>
+        <v>0.1107758758014892</v>
       </c>
       <c r="FB5" t="n">
-        <v>0.01676484058845156</v>
+        <v>0.01743914991076699</v>
       </c>
       <c r="FC5" t="n">
         <v>-0</v>
       </c>
       <c r="FD5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FE5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FF5" t="n">
         <v>-0</v>
       </c>
       <c r="FG5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FH5" t="n">
-        <v>0.05888160656207649</v>
+        <v>-0.04835713356947695</v>
       </c>
       <c r="FI5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FJ5" t="n">
-        <v>-0.04113637989789167</v>
+        <v>-0.04686937711619232</v>
       </c>
       <c r="FK5" t="n">
-        <v>0.006592493755074526</v>
+        <v>0.02543953856227785</v>
       </c>
       <c r="FL5" t="n">
         <v>-0</v>
@@ -3213,28 +3213,28 @@
         <v>0</v>
       </c>
       <c r="FN5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FO5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FP5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FQ5" t="n">
-        <v>-0.06189769889679061</v>
+        <v>0.01462615074853893</v>
       </c>
       <c r="FR5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FS5" t="n">
-        <v>0.04424033389894532</v>
+        <v>0.1362179520991598</v>
       </c>
       <c r="FT5" t="n">
-        <v>0.04809504894942038</v>
+        <v>-0.05905823685400256</v>
       </c>
       <c r="FU5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FV5" t="n">
         <v>-0</v>
@@ -3246,22 +3246,22 @@
         <v>0</v>
       </c>
       <c r="FY5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ5" t="n">
-        <v>-0.02258957145533626</v>
+        <v>-0.108066510143188</v>
       </c>
       <c r="GA5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GB5" t="n">
-        <v>-0.01471347501261546</v>
+        <v>0.06774889142601669</v>
       </c>
       <c r="GC5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GD5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GE5" t="n">
         <v>-0</v>
@@ -3275,22 +3275,22 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="B6" t="n">
-        <v>0.02159722478757762</v>
+        <v>0.03311448237163975</v>
       </c>
       <c r="C6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="D6" t="n">
         <v>0</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.009179157880373991</v>
+        <v>0.01844223243648183</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.005661247499787549</v>
+        <v>-0.0137532850474254</v>
       </c>
       <c r="G6" t="n">
         <v>0</v>
@@ -3302,25 +3302,25 @@
         <v>0</v>
       </c>
       <c r="J6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>0.006301539091212736</v>
+        <v>0.04323695185555432</v>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="M6" t="n">
         <v>0</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.01065844125691091</v>
+        <v>0.008937662222140501</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.00469519841731844</v>
+        <v>-0.008905393774096829</v>
       </c>
       <c r="P6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>
@@ -3329,10 +3329,10 @@
         <v>0</v>
       </c>
       <c r="S6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="T6" t="n">
-        <v>0.0002467519490243309</v>
+        <v>-0.0005799132781596862</v>
       </c>
       <c r="U6" t="n">
         <v>0</v>
@@ -3341,43 +3341,43 @@
         <v>0</v>
       </c>
       <c r="W6" t="n">
-        <v>-0.0006486229115706288</v>
+        <v>-0.002772732385476751</v>
       </c>
       <c r="X6" t="n">
-        <v>-0.00220321748667707</v>
+        <v>0.0002066176020104387</v>
       </c>
       <c r="Y6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z6" t="n">
         <v>0</v>
       </c>
       <c r="AA6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AB6" t="n">
         <v>-0</v>
       </c>
       <c r="AC6" t="n">
-        <v>0.0141254858674285</v>
+        <v>-0.01681759978587626</v>
       </c>
       <c r="AD6" t="n">
         <v>0</v>
       </c>
       <c r="AE6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AF6" t="n">
-        <v>0.01693771227155624</v>
+        <v>-0.05824699586748554</v>
       </c>
       <c r="AG6" t="n">
-        <v>0.0002701930637198651</v>
+        <v>-0.01677663855332415</v>
       </c>
       <c r="AH6" t="n">
         <v>0</v>
       </c>
       <c r="AI6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AJ6" t="n">
         <v>-0</v>
@@ -3386,49 +3386,49 @@
         <v>0</v>
       </c>
       <c r="AL6" t="n">
-        <v>0.003548661477288489</v>
+        <v>0.01007247417809857</v>
       </c>
       <c r="AM6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AN6" t="n">
         <v>0</v>
       </c>
       <c r="AO6" t="n">
-        <v>-0.01609488168767206</v>
+        <v>-0.01091138642776752</v>
       </c>
       <c r="AP6" t="n">
-        <v>-0.004127565803492772</v>
+        <v>-0.02108590915674383</v>
       </c>
       <c r="AQ6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AR6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AS6" t="n">
         <v>0</v>
       </c>
       <c r="AT6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AU6" t="n">
-        <v>0.04041583779387532</v>
+        <v>0.09552571578530783</v>
       </c>
       <c r="AV6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AW6" t="n">
         <v>0</v>
       </c>
       <c r="AX6" t="n">
-        <v>-0.009325599561948792</v>
+        <v>-0.01777964493294697</v>
       </c>
       <c r="AY6" t="n">
-        <v>-0.007680456602878511</v>
+        <v>-0.01827121136369252</v>
       </c>
       <c r="AZ6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BA6" t="n">
         <v>0</v>
@@ -3437,10 +3437,10 @@
         <v>-0</v>
       </c>
       <c r="BC6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BD6" t="n">
-        <v>0.004182740523848419</v>
+        <v>-0.004481194379833773</v>
       </c>
       <c r="BE6" t="n">
         <v>0</v>
@@ -3449,13 +3449,13 @@
         <v>0</v>
       </c>
       <c r="BG6" t="n">
-        <v>-0.00672299006793999</v>
+        <v>-0.006623680222492765</v>
       </c>
       <c r="BH6" t="n">
-        <v>0.001646281456453661</v>
+        <v>0.004710010803733601</v>
       </c>
       <c r="BI6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BJ6" t="n">
         <v>0</v>
@@ -3464,37 +3464,37 @@
         <v>0</v>
       </c>
       <c r="BL6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BM6" t="n">
-        <v>0.02454108188237956</v>
+        <v>0.01747737522704056</v>
       </c>
       <c r="BN6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BO6" t="n">
         <v>-0</v>
       </c>
       <c r="BP6" t="n">
-        <v>0.01355932034501056</v>
+        <v>0.04028674454082552</v>
       </c>
       <c r="BQ6" t="n">
-        <v>0.01042683503452683</v>
+        <v>0.03348743546264912</v>
       </c>
       <c r="BR6" t="n">
         <v>-0</v>
       </c>
       <c r="BS6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BT6" t="n">
         <v>0</v>
       </c>
       <c r="BU6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BV6" t="n">
-        <v>0.01490065229342337</v>
+        <v>0.03972042410553178</v>
       </c>
       <c r="BW6" t="n">
         <v>0</v>
@@ -3503,13 +3503,13 @@
         <v>0</v>
       </c>
       <c r="BY6" t="n">
-        <v>-0.008192042503298474</v>
+        <v>0.0007388326991219912</v>
       </c>
       <c r="BZ6" t="n">
-        <v>0.01736663990601979</v>
+        <v>-0.03736479450301312</v>
       </c>
       <c r="CA6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CB6" t="n">
         <v>0</v>
@@ -3521,76 +3521,76 @@
         <v>-0</v>
       </c>
       <c r="CE6" t="n">
-        <v>-0.0003574973787048697</v>
+        <v>-0.010026814272848</v>
       </c>
       <c r="CF6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CG6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CH6" t="n">
-        <v>0.0004504690255603935</v>
+        <v>-0.001995127022735481</v>
       </c>
       <c r="CI6" t="n">
-        <v>0.005104835806897838</v>
+        <v>0.02397661215467053</v>
       </c>
       <c r="CJ6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CK6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CL6" t="n">
         <v>-0</v>
       </c>
       <c r="CM6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CN6" t="n">
-        <v>0.0010041531622763</v>
+        <v>-0.03295670176918961</v>
       </c>
       <c r="CO6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CP6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CQ6" t="n">
-        <v>-0.0003231949942139965</v>
+        <v>0.04324470406127795</v>
       </c>
       <c r="CR6" t="n">
-        <v>-0.01454028693444777</v>
+        <v>0.02712275334971945</v>
       </c>
       <c r="CS6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CT6" t="n">
         <v>-0</v>
       </c>
       <c r="CU6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CV6" t="n">
         <v>0</v>
       </c>
       <c r="CW6" t="n">
-        <v>0.003033047092561521</v>
+        <v>-0.01273319109713205</v>
       </c>
       <c r="CX6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CY6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CZ6" t="n">
-        <v>0.001562471905302228</v>
+        <v>-0.003752562814351805</v>
       </c>
       <c r="DA6" t="n">
-        <v>0.00489759121985708</v>
+        <v>0.02134261515535393</v>
       </c>
       <c r="DB6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DC6" t="n">
         <v>0</v>
@@ -3599,22 +3599,22 @@
         <v>0</v>
       </c>
       <c r="DE6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DF6" t="n">
-        <v>0.001375168397106817</v>
+        <v>-0.0150679179466528</v>
       </c>
       <c r="DG6" t="n">
         <v>-0</v>
       </c>
       <c r="DH6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DI6" t="n">
-        <v>-0.0001156717608161516</v>
+        <v>-0.001000000177936354</v>
       </c>
       <c r="DJ6" t="n">
-        <v>0.01500791352857555</v>
+        <v>-0.004998133507418673</v>
       </c>
       <c r="DK6" t="n">
         <v>0</v>
@@ -3623,40 +3623,40 @@
         <v>-0</v>
       </c>
       <c r="DM6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DN6" t="n">
         <v>-0</v>
       </c>
       <c r="DO6" t="n">
-        <v>0.002722164748011138</v>
+        <v>-0.01466611625303083</v>
       </c>
       <c r="DP6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DQ6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DR6" t="n">
-        <v>0.01362850124383482</v>
+        <v>0.0009670422578939217</v>
       </c>
       <c r="DS6" t="n">
-        <v>0.001414206756607409</v>
+        <v>0.03199345123638533</v>
       </c>
       <c r="DT6" t="n">
         <v>-0</v>
       </c>
       <c r="DU6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DV6" t="n">
         <v>-0</v>
       </c>
       <c r="DW6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DX6" t="n">
-        <v>-0.01290100985135379</v>
+        <v>-0.01261551876286441</v>
       </c>
       <c r="DY6" t="n">
         <v>0</v>
@@ -3665,64 +3665,64 @@
         <v>-0</v>
       </c>
       <c r="EA6" t="n">
-        <v>-0.008453315728178985</v>
+        <v>0.002393676437939063</v>
       </c>
       <c r="EB6" t="n">
-        <v>-0.0002644793583403722</v>
+        <v>0.02452855118934899</v>
       </c>
       <c r="EC6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ED6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EE6" t="n">
         <v>-0</v>
       </c>
       <c r="EF6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EG6" t="n">
-        <v>0.00307624606809338</v>
+        <v>-0.0107022511239365</v>
       </c>
       <c r="EH6" t="n">
         <v>-0</v>
       </c>
       <c r="EI6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EJ6" t="n">
-        <v>0.001829521801082525</v>
+        <v>-0.02018182221309976</v>
       </c>
       <c r="EK6" t="n">
-        <v>0.00363354340332819</v>
+        <v>0.003265028477087621</v>
       </c>
       <c r="EL6" t="n">
         <v>-0</v>
       </c>
       <c r="EM6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EN6" t="n">
         <v>-0</v>
       </c>
       <c r="EO6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EP6" t="n">
-        <v>0.0001071239190760733</v>
+        <v>0.0009326937568919222</v>
       </c>
       <c r="EQ6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ER6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ES6" t="n">
-        <v>-0.01136488398234254</v>
+        <v>-0.002136503028500973</v>
       </c>
       <c r="ET6" t="n">
-        <v>0.03151982086563588</v>
+        <v>0.01498678542284139</v>
       </c>
       <c r="EU6" t="n">
         <v>0</v>
@@ -3731,28 +3731,28 @@
         <v>0</v>
       </c>
       <c r="EW6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EX6" t="n">
         <v>-0</v>
       </c>
       <c r="EY6" t="n">
-        <v>0.004462169002380318</v>
+        <v>-0.01631066439118388</v>
       </c>
       <c r="EZ6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FA6" t="n">
         <v>0</v>
       </c>
       <c r="FB6" t="n">
-        <v>0.001705063750737298</v>
+        <v>-0.009049737715356694</v>
       </c>
       <c r="FC6" t="n">
-        <v>0.007523914521820521</v>
+        <v>0.01558315359310781</v>
       </c>
       <c r="FD6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FE6" t="n">
         <v>-0</v>
@@ -3761,22 +3761,22 @@
         <v>-0</v>
       </c>
       <c r="FG6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FH6" t="n">
-        <v>-0.009506322505821582</v>
+        <v>-0.019685474350425</v>
       </c>
       <c r="FI6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FJ6" t="n">
         <v>-0</v>
       </c>
       <c r="FK6" t="n">
-        <v>-0.01376227990403237</v>
+        <v>0.01468516486181659</v>
       </c>
       <c r="FL6" t="n">
-        <v>0.02299860867621803</v>
+        <v>0.00558800094221256</v>
       </c>
       <c r="FM6" t="n">
         <v>0</v>
@@ -3785,13 +3785,13 @@
         <v>-0</v>
       </c>
       <c r="FO6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FP6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FQ6" t="n">
-        <v>-0.007621392672338096</v>
+        <v>0.01574578763771254</v>
       </c>
       <c r="FR6" t="n">
         <v>-0</v>
@@ -3800,10 +3800,10 @@
         <v>-0</v>
       </c>
       <c r="FT6" t="n">
-        <v>0.0008004711905588321</v>
+        <v>0.002762841738128972</v>
       </c>
       <c r="FU6" t="n">
-        <v>0.000484966604608691</v>
+        <v>-0.03033170268187956</v>
       </c>
       <c r="FV6" t="n">
         <v>-0</v>
@@ -3812,31 +3812,31 @@
         <v>-0</v>
       </c>
       <c r="FX6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FY6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ6" t="n">
-        <v>-0.01702483983139819</v>
+        <v>0.01094027241117791</v>
       </c>
       <c r="GA6" t="n">
         <v>0</v>
       </c>
       <c r="GB6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GC6" t="n">
         <v>-0</v>
       </c>
       <c r="GD6" t="n">
-        <v>-0.004899496553851967</v>
+        <v>0.01677227857008068</v>
       </c>
       <c r="GE6" t="n">
         <v>0</v>
       </c>
       <c r="GF6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GG6" t="n">
         <v>0</v>
@@ -3847,7 +3847,7 @@
         <v>0</v>
       </c>
       <c r="B7" t="n">
-        <v>0.1031801412830552</v>
+        <v>0.05546987461659386</v>
       </c>
       <c r="C7" t="n">
         <v>0</v>
@@ -3856,25 +3856,25 @@
         <v>0</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.0169415303009093</v>
+        <v>-0.0259740623148672</v>
       </c>
       <c r="F7" t="n">
         <v>0</v>
       </c>
       <c r="G7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="H7" t="n">
         <v>-0</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.01507377107400712</v>
+        <v>-0.005578317650135636</v>
       </c>
       <c r="J7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="K7" t="n">
-        <v>0.03960646893092429</v>
+        <v>0.06404445954781476</v>
       </c>
       <c r="L7" t="n">
         <v>-0</v>
@@ -3883,7 +3883,7 @@
         <v>0</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.05216377527772087</v>
+        <v>-0.02296179566048659</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -3892,16 +3892,16 @@
         <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="R7" t="n">
-        <v>-0.01179029845624995</v>
+        <v>-0.003001099908165418</v>
       </c>
       <c r="S7" t="n">
         <v>-0</v>
       </c>
       <c r="T7" t="n">
-        <v>0.004931518428212159</v>
+        <v>-0.002511245104952005</v>
       </c>
       <c r="U7" t="n">
         <v>-0</v>
@@ -3910,34 +3910,34 @@
         <v>0</v>
       </c>
       <c r="W7" t="n">
-        <v>-0.002183330308766976</v>
+        <v>-0.006026773111834845</v>
       </c>
       <c r="X7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA7" t="n">
-        <v>-8.264624820606789e-05</v>
+        <v>0.0005066512176523189</v>
       </c>
       <c r="AB7" t="n">
         <v>-0</v>
       </c>
       <c r="AC7" t="n">
-        <v>0.03932881231466817</v>
+        <v>-0.0144021665088775</v>
       </c>
       <c r="AD7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AE7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AF7" t="n">
-        <v>0.02884918326669116</v>
+        <v>-0.01943324151890779</v>
       </c>
       <c r="AG7" t="n">
         <v>0</v>
@@ -3946,16 +3946,16 @@
         <v>0</v>
       </c>
       <c r="AI7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AJ7" t="n">
-        <v>0.01519395864318696</v>
+        <v>-0.000639257259422425</v>
       </c>
       <c r="AK7" t="n">
         <v>0</v>
       </c>
       <c r="AL7" t="n">
-        <v>0.02430499248857348</v>
+        <v>0.02251692348152725</v>
       </c>
       <c r="AM7" t="n">
         <v>0</v>
@@ -3964,37 +3964,37 @@
         <v>0</v>
       </c>
       <c r="AO7" t="n">
-        <v>-0.02257605803588043</v>
+        <v>-0.00783913857994005</v>
       </c>
       <c r="AP7" t="n">
         <v>0</v>
       </c>
       <c r="AQ7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AR7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AS7" t="n">
-        <v>-0.01377245530718949</v>
+        <v>-0.004156358258548553</v>
       </c>
       <c r="AT7" t="n">
         <v>-0</v>
       </c>
       <c r="AU7" t="n">
-        <v>0.1865013695318965</v>
+        <v>0.0986635233607291</v>
       </c>
       <c r="AV7" t="n">
         <v>-0</v>
       </c>
       <c r="AW7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AX7" t="n">
-        <v>0.07130917342078245</v>
+        <v>-0.01950710249445866</v>
       </c>
       <c r="AY7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AZ7" t="n">
         <v>0</v>
@@ -4003,13 +4003,13 @@
         <v>0</v>
       </c>
       <c r="BB7" t="n">
-        <v>0.0004078744567606258</v>
+        <v>0.01113688222188637</v>
       </c>
       <c r="BC7" t="n">
         <v>0</v>
       </c>
       <c r="BD7" t="n">
-        <v>-0.01045296593584606</v>
+        <v>-0.003070374664013226</v>
       </c>
       <c r="BE7" t="n">
         <v>0</v>
@@ -4018,79 +4018,79 @@
         <v>0</v>
       </c>
       <c r="BG7" t="n">
-        <v>-0.03456112894570643</v>
+        <v>-0.01174349705709851</v>
       </c>
       <c r="BH7" t="n">
         <v>0</v>
       </c>
       <c r="BI7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BJ7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BK7" t="n">
-        <v>0.01364664912013745</v>
+        <v>0.008220974666818353</v>
       </c>
       <c r="BL7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BM7" t="n">
-        <v>0.01791154447235991</v>
+        <v>0.0143426980872776</v>
       </c>
       <c r="BN7" t="n">
         <v>-0</v>
       </c>
       <c r="BO7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BP7" t="n">
-        <v>0.07985008796711453</v>
+        <v>0.03929972356908592</v>
       </c>
       <c r="BQ7" t="n">
         <v>-0</v>
       </c>
       <c r="BR7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BS7" t="n">
         <v>-0</v>
       </c>
       <c r="BT7" t="n">
-        <v>0.02764628945089632</v>
+        <v>0.01298072466692995</v>
       </c>
       <c r="BU7" t="n">
         <v>-0</v>
       </c>
       <c r="BV7" t="n">
-        <v>0.09516154712953992</v>
+        <v>0.05249046795288398</v>
       </c>
       <c r="BW7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BX7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BY7" t="n">
-        <v>0.01030281724130517</v>
+        <v>-0.02346371463265612</v>
       </c>
       <c r="BZ7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CA7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CB7" t="n">
         <v>0</v>
       </c>
       <c r="CC7" t="n">
-        <v>0.01097004661860797</v>
+        <v>-0.01727355857484623</v>
       </c>
       <c r="CD7" t="n">
         <v>-0</v>
       </c>
       <c r="CE7" t="n">
-        <v>-0.02219033599814732</v>
+        <v>-0.02348877720288143</v>
       </c>
       <c r="CF7" t="n">
         <v>-0</v>
@@ -4099,10 +4099,10 @@
         <v>-0</v>
       </c>
       <c r="CH7" t="n">
-        <v>0.0006302887975269791</v>
+        <v>0.009467110927672742</v>
       </c>
       <c r="CI7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CJ7" t="n">
         <v>-0</v>
@@ -4111,25 +4111,25 @@
         <v>0</v>
       </c>
       <c r="CL7" t="n">
-        <v>0.02740800371112031</v>
+        <v>0.01205704021346352</v>
       </c>
       <c r="CM7" t="n">
         <v>0</v>
       </c>
       <c r="CN7" t="n">
-        <v>-0.02191390521925252</v>
+        <v>-0.04393883831337543</v>
       </c>
       <c r="CO7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CP7" t="n">
         <v>-0</v>
       </c>
       <c r="CQ7" t="n">
-        <v>-0.02024696479653388</v>
+        <v>0.007165393371776697</v>
       </c>
       <c r="CR7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CS7" t="n">
         <v>-0</v>
@@ -4138,13 +4138,13 @@
         <v>-0</v>
       </c>
       <c r="CU7" t="n">
-        <v>-0.01075862280965435</v>
+        <v>0.01791840313390215</v>
       </c>
       <c r="CV7" t="n">
         <v>0</v>
       </c>
       <c r="CW7" t="n">
-        <v>-0.0177691205069412</v>
+        <v>-0.02437779077417179</v>
       </c>
       <c r="CX7" t="n">
         <v>0</v>
@@ -4153,34 +4153,34 @@
         <v>0</v>
       </c>
       <c r="CZ7" t="n">
-        <v>0.00669667301277503</v>
+        <v>0.005266318044248815</v>
       </c>
       <c r="DA7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DB7" t="n">
         <v>0</v>
       </c>
       <c r="DC7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DD7" t="n">
-        <v>0.0270905324334753</v>
+        <v>0.01120499920581262</v>
       </c>
       <c r="DE7" t="n">
         <v>0</v>
       </c>
       <c r="DF7" t="n">
-        <v>-0.07473088078366658</v>
+        <v>-0.01805087686459666</v>
       </c>
       <c r="DG7" t="n">
         <v>-0</v>
       </c>
       <c r="DH7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DI7" t="n">
-        <v>0.02815623067696025</v>
+        <v>-0.01143379628296896</v>
       </c>
       <c r="DJ7" t="n">
         <v>-0</v>
@@ -4189,97 +4189,97 @@
         <v>0</v>
       </c>
       <c r="DL7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DM7" t="n">
-        <v>-0.007883091174375668</v>
+        <v>-0.008657146617649696</v>
       </c>
       <c r="DN7" t="n">
         <v>-0</v>
       </c>
       <c r="DO7" t="n">
-        <v>0.0024515701484624</v>
+        <v>-0.01905747665061474</v>
       </c>
       <c r="DP7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DQ7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DR7" t="n">
-        <v>-0.005883578955597431</v>
+        <v>0.009636444115872798</v>
       </c>
       <c r="DS7" t="n">
         <v>-0</v>
       </c>
       <c r="DT7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DU7" t="n">
         <v>-0</v>
       </c>
       <c r="DV7" t="n">
-        <v>-5.499776242723439e-05</v>
+        <v>-0.02853741733525758</v>
       </c>
       <c r="DW7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DX7" t="n">
-        <v>-0.001148386657213948</v>
+        <v>0.008625568079226357</v>
       </c>
       <c r="DY7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DZ7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EA7" t="n">
-        <v>-0.01651198217408619</v>
+        <v>0.007035845911457121</v>
       </c>
       <c r="EB7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EC7" t="n">
         <v>-0</v>
       </c>
       <c r="ED7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EE7" t="n">
-        <v>-0.009233625603536872</v>
+        <v>-0.007593690724758079</v>
       </c>
       <c r="EF7" t="n">
         <v>0</v>
       </c>
       <c r="EG7" t="n">
-        <v>-0.002987902293173323</v>
+        <v>-0.01939422681251175</v>
       </c>
       <c r="EH7" t="n">
         <v>0</v>
       </c>
       <c r="EI7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EJ7" t="n">
-        <v>0.03177338330147627</v>
+        <v>0.001406658346303996</v>
       </c>
       <c r="EK7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EL7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EM7" t="n">
         <v>0</v>
       </c>
       <c r="EN7" t="n">
-        <v>0.02936001172798325</v>
+        <v>0.004862560852454835</v>
       </c>
       <c r="EO7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EP7" t="n">
-        <v>-0.03740327569084578</v>
+        <v>-0.004014177148971523</v>
       </c>
       <c r="EQ7" t="n">
         <v>-0</v>
@@ -4288,25 +4288,25 @@
         <v>-0</v>
       </c>
       <c r="ES7" t="n">
-        <v>-0.002531081942838193</v>
+        <v>0.006205319364446583</v>
       </c>
       <c r="ET7" t="n">
         <v>-0</v>
       </c>
       <c r="EU7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EV7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EW7" t="n">
-        <v>0.01091833980878158</v>
+        <v>0.007138275955903084</v>
       </c>
       <c r="EX7" t="n">
         <v>-0</v>
       </c>
       <c r="EY7" t="n">
-        <v>-0.02935791363429257</v>
+        <v>-0.02811001335025314</v>
       </c>
       <c r="EZ7" t="n">
         <v>-0</v>
@@ -4315,7 +4315,7 @@
         <v>-0</v>
       </c>
       <c r="FB7" t="n">
-        <v>0.006806085179199716</v>
+        <v>0.002275657634629206</v>
       </c>
       <c r="FC7" t="n">
         <v>-0</v>
@@ -4327,40 +4327,40 @@
         <v>0</v>
       </c>
       <c r="FF7" t="n">
-        <v>0.01543978374806084</v>
+        <v>0.01206940206644274</v>
       </c>
       <c r="FG7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FH7" t="n">
-        <v>-0.02938303722446956</v>
+        <v>-0.017267744171386</v>
       </c>
       <c r="FI7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FJ7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FK7" t="n">
-        <v>-0.02288714874275935</v>
+        <v>0.008220439181277918</v>
       </c>
       <c r="FL7" t="n">
         <v>0</v>
       </c>
       <c r="FM7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FN7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FO7" t="n">
-        <v>0.01262761137798691</v>
+        <v>0.04042896413973883</v>
       </c>
       <c r="FP7" t="n">
         <v>-0</v>
       </c>
       <c r="FQ7" t="n">
-        <v>-0.0501811896263641</v>
+        <v>0.008998167610409653</v>
       </c>
       <c r="FR7" t="n">
         <v>-0</v>
@@ -4369,7 +4369,7 @@
         <v>-0</v>
       </c>
       <c r="FT7" t="n">
-        <v>0.01490191710335407</v>
+        <v>-0.01733821610149014</v>
       </c>
       <c r="FU7" t="n">
         <v>0</v>
@@ -4381,16 +4381,16 @@
         <v>-0</v>
       </c>
       <c r="FX7" t="n">
-        <v>0.0002643116241766197</v>
+        <v>0.00180354632266044</v>
       </c>
       <c r="FY7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ7" t="n">
-        <v>-0.03655693194673591</v>
+        <v>-0.01148425258189587</v>
       </c>
       <c r="GA7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GB7" t="n">
         <v>-0</v>
@@ -4399,16 +4399,16 @@
         <v>0</v>
       </c>
       <c r="GD7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GE7" t="n">
         <v>-0</v>
       </c>
       <c r="GF7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GG7" t="n">
-        <v>0.03445207037953209</v>
+        <v>0.001766596970740732</v>
       </c>
     </row>
     <row r="8">
@@ -4985,22 +4985,22 @@
         <v>0</v>
       </c>
       <c r="B9" t="n">
-        <v>0.2319029384254359</v>
+        <v>0.186954513384348</v>
       </c>
       <c r="C9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.1107771709869047</v>
+        <v>-0.1100043358679616</v>
       </c>
       <c r="E9" t="n">
-        <v>0.01045162339046189</v>
+        <v>-0.04304419255367406</v>
       </c>
       <c r="F9" t="n">
         <v>0</v>
       </c>
       <c r="G9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="H9" t="n">
         <v>-0</v>
@@ -5012,43 +5012,43 @@
         <v>-0</v>
       </c>
       <c r="K9" t="n">
-        <v>0.1156994697951736</v>
+        <v>0.150502223613522</v>
       </c>
       <c r="L9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.0969347805171662</v>
+        <v>-0.1240575043716689</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.03940470545214244</v>
+        <v>-0.08692324210701508</v>
       </c>
       <c r="O9" t="n">
         <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Q9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
         <v>0</v>
       </c>
       <c r="S9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="T9" t="n">
-        <v>0.0323178882973082</v>
+        <v>0.03443102930799952</v>
       </c>
       <c r="U9" t="n">
         <v>-0</v>
       </c>
       <c r="V9" t="n">
-        <v>0.007825114509000898</v>
+        <v>-0.005068119864751338</v>
       </c>
       <c r="W9" t="n">
-        <v>0.005917648367243545</v>
+        <v>-0.02028079044170974</v>
       </c>
       <c r="X9" t="n">
         <v>0</v>
@@ -5057,52 +5057,52 @@
         <v>-0</v>
       </c>
       <c r="Z9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AB9" t="n">
         <v>-0</v>
       </c>
       <c r="AC9" t="n">
-        <v>0.1301858102883915</v>
+        <v>-0.007253078616780379</v>
       </c>
       <c r="AD9" t="n">
         <v>0</v>
       </c>
       <c r="AE9" t="n">
-        <v>-0.06117354050955786</v>
+        <v>-0.08263590291427481</v>
       </c>
       <c r="AF9" t="n">
-        <v>0.02451385287814362</v>
+        <v>-0.1119277791433214</v>
       </c>
       <c r="AG9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AH9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AI9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AJ9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AK9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AL9" t="n">
-        <v>-0.015841074903792</v>
+        <v>0.1365635353773277</v>
       </c>
       <c r="AM9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AN9" t="n">
-        <v>-0.0354423252561731</v>
+        <v>-0.06906927888518827</v>
       </c>
       <c r="AO9" t="n">
-        <v>-0.08531715456739</v>
+        <v>0.05384050227039958</v>
       </c>
       <c r="AP9" t="n">
         <v>0</v>
@@ -5111,31 +5111,31 @@
         <v>0</v>
       </c>
       <c r="AR9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AS9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AT9" t="n">
         <v>-0</v>
       </c>
       <c r="AU9" t="n">
-        <v>0.374191283563395</v>
+        <v>0.2407777933037444</v>
       </c>
       <c r="AV9" t="n">
         <v>-0</v>
       </c>
       <c r="AW9" t="n">
-        <v>0.03392129531290469</v>
+        <v>-0.05875698188868149</v>
       </c>
       <c r="AX9" t="n">
-        <v>0.2264814004537224</v>
+        <v>-0.2973479882885797</v>
       </c>
       <c r="AY9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AZ9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BA9" t="n">
         <v>0</v>
@@ -5147,16 +5147,16 @@
         <v>-0</v>
       </c>
       <c r="BD9" t="n">
-        <v>-0.0009724321381377078</v>
+        <v>-0.03340579645520284</v>
       </c>
       <c r="BE9" t="n">
         <v>0</v>
       </c>
       <c r="BF9" t="n">
-        <v>-0.04190626428043825</v>
+        <v>-0.01099215810808823</v>
       </c>
       <c r="BG9" t="n">
-        <v>-0.08474454504850373</v>
+        <v>0.01488704551571974</v>
       </c>
       <c r="BH9" t="n">
         <v>0</v>
@@ -5165,7 +5165,7 @@
         <v>-0</v>
       </c>
       <c r="BJ9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BK9" t="n">
         <v>0</v>
@@ -5174,22 +5174,22 @@
         <v>-0</v>
       </c>
       <c r="BM9" t="n">
-        <v>0.1566594924467971</v>
+        <v>0.03421105598772972</v>
       </c>
       <c r="BN9" t="n">
         <v>-0</v>
       </c>
       <c r="BO9" t="n">
-        <v>0.01916363040518941</v>
+        <v>0.01305582377881617</v>
       </c>
       <c r="BP9" t="n">
-        <v>0.147745654978383</v>
+        <v>0.03179687712862066</v>
       </c>
       <c r="BQ9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BR9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BS9" t="n">
         <v>-0</v>
@@ -5201,22 +5201,22 @@
         <v>-0</v>
       </c>
       <c r="BV9" t="n">
-        <v>0.1954355089824316</v>
+        <v>0.2179828688217849</v>
       </c>
       <c r="BW9" t="n">
         <v>0</v>
       </c>
       <c r="BX9" t="n">
-        <v>0.02936648249185378</v>
+        <v>-0.161275911383101</v>
       </c>
       <c r="BY9" t="n">
-        <v>0.0677276580256902</v>
+        <v>-0.08779792137256361</v>
       </c>
       <c r="BZ9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CA9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CB9" t="n">
         <v>0</v>
@@ -5228,25 +5228,25 @@
         <v>-0</v>
       </c>
       <c r="CE9" t="n">
-        <v>-0.05511880174412279</v>
+        <v>-0.07489527905795566</v>
       </c>
       <c r="CF9" t="n">
         <v>-0</v>
       </c>
       <c r="CG9" t="n">
-        <v>0.002538104076607804</v>
+        <v>0.1013448167016057</v>
       </c>
       <c r="CH9" t="n">
-        <v>-0.01736869774855941</v>
+        <v>0.02727710012932164</v>
       </c>
       <c r="CI9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CJ9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CK9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CL9" t="n">
         <v>-0</v>
@@ -5255,25 +5255,25 @@
         <v>0</v>
       </c>
       <c r="CN9" t="n">
-        <v>-0.08251095067026529</v>
+        <v>-0.08263924867294349</v>
       </c>
       <c r="CO9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CP9" t="n">
-        <v>-0.1242065704104098</v>
+        <v>0.2653007931985885</v>
       </c>
       <c r="CQ9" t="n">
-        <v>-0.09559533007684799</v>
+        <v>0.1245383188790891</v>
       </c>
       <c r="CR9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CS9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CT9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CU9" t="n">
         <v>-0</v>
@@ -5282,25 +5282,25 @@
         <v>0</v>
       </c>
       <c r="CW9" t="n">
-        <v>-0.02868901060355702</v>
+        <v>-0.05634467017539579</v>
       </c>
       <c r="CX9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CY9" t="n">
-        <v>0.02170397893328013</v>
+        <v>0.1133158842456859</v>
       </c>
       <c r="CZ9" t="n">
-        <v>-0.006815353181409908</v>
+        <v>0.04662473697084415</v>
       </c>
       <c r="DA9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DB9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DC9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DD9" t="n">
         <v>0</v>
@@ -5309,22 +5309,22 @@
         <v>-0</v>
       </c>
       <c r="DF9" t="n">
-        <v>-0.01771918938706324</v>
+        <v>-0.007633207974636284</v>
       </c>
       <c r="DG9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DH9" t="n">
-        <v>0.008374083876259054</v>
+        <v>0.01797733241987125</v>
       </c>
       <c r="DI9" t="n">
-        <v>0.0282165899660476</v>
+        <v>-0.04066466883422259</v>
       </c>
       <c r="DJ9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DK9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DL9" t="n">
         <v>0</v>
@@ -5336,106 +5336,106 @@
         <v>-0</v>
       </c>
       <c r="DO9" t="n">
-        <v>-0.0600284238804587</v>
+        <v>-0.08345177372333107</v>
       </c>
       <c r="DP9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DQ9" t="n">
-        <v>-0.05064262848990792</v>
+        <v>0.07707116746093048</v>
       </c>
       <c r="DR9" t="n">
-        <v>-0.0004602697032325897</v>
+        <v>0.02298430991150134</v>
       </c>
       <c r="DS9" t="n">
         <v>0</v>
       </c>
       <c r="DT9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DU9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DV9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DW9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DX9" t="n">
-        <v>0.03786733559509122</v>
+        <v>0.01393416504186675</v>
       </c>
       <c r="DY9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DZ9" t="n">
-        <v>-0.03549986617917782</v>
+        <v>0.04816451384754736</v>
       </c>
       <c r="EA9" t="n">
-        <v>-0.01242780066420288</v>
+        <v>-0.03988523216025391</v>
       </c>
       <c r="EB9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EC9" t="n">
         <v>0</v>
       </c>
       <c r="ED9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EE9" t="n">
         <v>-0</v>
       </c>
       <c r="EF9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EG9" t="n">
-        <v>0.001947499195706141</v>
+        <v>0.01192291175927758</v>
       </c>
       <c r="EH9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EI9" t="n">
-        <v>0.05587069726941786</v>
+        <v>0.06846846423522343</v>
       </c>
       <c r="EJ9" t="n">
-        <v>0.04484614684632397</v>
+        <v>0.04072493904567681</v>
       </c>
       <c r="EK9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EL9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EM9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EN9" t="n">
         <v>-0</v>
       </c>
       <c r="EO9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EP9" t="n">
-        <v>-0.07196612669216734</v>
+        <v>-0.07749269450548739</v>
       </c>
       <c r="EQ9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="ER9" t="n">
-        <v>-0.06055884831520146</v>
+        <v>-0.08437319566498813</v>
       </c>
       <c r="ES9" t="n">
-        <v>-0.003370468211697274</v>
+        <v>0.007763816209436732</v>
       </c>
       <c r="ET9" t="n">
         <v>-0</v>
       </c>
       <c r="EU9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EV9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EW9" t="n">
         <v>-0</v>
@@ -5444,106 +5444,106 @@
         <v>-0</v>
       </c>
       <c r="EY9" t="n">
-        <v>-0.0431375468376183</v>
+        <v>-0.07530848904453155</v>
       </c>
       <c r="EZ9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FA9" t="n">
-        <v>0.01169547112632406</v>
+        <v>0.1283502246316171</v>
       </c>
       <c r="FB9" t="n">
-        <v>0.01081490133163081</v>
+        <v>0.02564464443888044</v>
       </c>
       <c r="FC9" t="n">
         <v>-0</v>
       </c>
       <c r="FD9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FE9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FF9" t="n">
         <v>-0</v>
       </c>
       <c r="FG9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FH9" t="n">
-        <v>0.0687488242460178</v>
+        <v>-0.02520658525889303</v>
       </c>
       <c r="FI9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FJ9" t="n">
-        <v>0.02500520376894284</v>
+        <v>0.02324200407655954</v>
       </c>
       <c r="FK9" t="n">
-        <v>-0.008261540386391614</v>
+        <v>-0.04396549348617066</v>
       </c>
       <c r="FL9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FM9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FN9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FO9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FP9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FQ9" t="n">
-        <v>-0.0682870327594966</v>
+        <v>0.01576762282339421</v>
       </c>
       <c r="FR9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FS9" t="n">
-        <v>-0.05920215023833851</v>
+        <v>0.1224067326066352</v>
       </c>
       <c r="FT9" t="n">
-        <v>0.1012729737675174</v>
+        <v>-0.1375260596562012</v>
       </c>
       <c r="FU9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FV9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FW9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FX9" t="n">
         <v>0</v>
       </c>
       <c r="FY9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ9" t="n">
-        <v>-0.03411875816083744</v>
+        <v>-0.01341374160173031</v>
       </c>
       <c r="GA9" t="n">
         <v>-0</v>
       </c>
       <c r="GB9" t="n">
-        <v>-0.07640376375669169</v>
+        <v>0.04440936383685353</v>
       </c>
       <c r="GC9" t="n">
         <v>0</v>
       </c>
       <c r="GD9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GE9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GF9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GG9" t="n">
         <v>0</v>
@@ -5554,16 +5554,16 @@
         <v>0</v>
       </c>
       <c r="B10" t="n">
-        <v>0.3710338248747325</v>
+        <v>0.2241379504448847</v>
       </c>
       <c r="C10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.1524286601177906</v>
+        <v>-0.2269707679480559</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.1221710332137563</v>
+        <v>-0.1316975060318737</v>
       </c>
       <c r="F10" t="n">
         <v>0</v>
@@ -5572,7 +5572,7 @@
         <v>-0</v>
       </c>
       <c r="H10" t="n">
-        <v>0.004445822156029789</v>
+        <v>0.01506712843299399</v>
       </c>
       <c r="I10" t="n">
         <v>-0</v>
@@ -5581,16 +5581,16 @@
         <v>-0</v>
       </c>
       <c r="K10" t="n">
-        <v>0.1993566183833969</v>
+        <v>0.1765858973194063</v>
       </c>
       <c r="L10" t="n">
         <v>-0</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.1080256313473331</v>
+        <v>-0.2198591195462458</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.1845815996800157</v>
+        <v>-0.1696807752524015</v>
       </c>
       <c r="O10" t="n">
         <v>0</v>
@@ -5599,115 +5599,115 @@
         <v>-0</v>
       </c>
       <c r="Q10" t="n">
-        <v>-0.0007907772715027914</v>
+        <v>-0.000693571758476973</v>
       </c>
       <c r="R10" t="n">
         <v>-0</v>
       </c>
       <c r="S10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="T10" t="n">
-        <v>0.09266727722819403</v>
+        <v>0.07534188099047393</v>
       </c>
       <c r="U10" t="n">
         <v>-0</v>
       </c>
       <c r="V10" t="n">
-        <v>-0.02434287646005297</v>
+        <v>-0.03432203644098283</v>
       </c>
       <c r="W10" t="n">
-        <v>-0.0008931249223099286</v>
+        <v>-0.08552099306448044</v>
       </c>
       <c r="X10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Y10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z10" t="n">
-        <v>-8.555880679462096e-05</v>
+        <v>0.001266541635504327</v>
       </c>
       <c r="AA10" t="n">
         <v>-0</v>
       </c>
       <c r="AB10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AC10" t="n">
-        <v>0.09226941165676168</v>
+        <v>-0.1075577750888126</v>
       </c>
       <c r="AD10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AE10" t="n">
-        <v>0.07962733883044951</v>
+        <v>-0.04935758031167335</v>
       </c>
       <c r="AF10" t="n">
-        <v>-0.03269168688147394</v>
+        <v>-0.1638380443778049</v>
       </c>
       <c r="AG10" t="n">
         <v>0</v>
       </c>
       <c r="AH10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AI10" t="n">
-        <v>0.01466329606399533</v>
+        <v>0.0371492590607096</v>
       </c>
       <c r="AJ10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AK10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AL10" t="n">
-        <v>0.01542555702705662</v>
+        <v>0.1192247571787542</v>
       </c>
       <c r="AM10" t="n">
         <v>-0</v>
       </c>
       <c r="AN10" t="n">
-        <v>-0.05197987034059726</v>
+        <v>-0.02287145373009319</v>
       </c>
       <c r="AO10" t="n">
-        <v>-0.08196481392612195</v>
+        <v>0.038684049248814</v>
       </c>
       <c r="AP10" t="n">
         <v>0</v>
       </c>
       <c r="AQ10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AR10" t="n">
-        <v>0.009561916419371713</v>
+        <v>0.01154072327917104</v>
       </c>
       <c r="AS10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AT10" t="n">
         <v>-0</v>
       </c>
       <c r="AU10" t="n">
-        <v>0.5728539666415917</v>
+        <v>0.2663791497411229</v>
       </c>
       <c r="AV10" t="n">
         <v>-0</v>
       </c>
       <c r="AW10" t="n">
-        <v>-0.002213277197935295</v>
+        <v>-0.07682929411458357</v>
       </c>
       <c r="AX10" t="n">
-        <v>0.2020146268286124</v>
+        <v>-0.3604364099018396</v>
       </c>
       <c r="AY10" t="n">
         <v>-0</v>
       </c>
       <c r="AZ10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BA10" t="n">
-        <v>0.06469522502050286</v>
+        <v>-0.0691982990548862</v>
       </c>
       <c r="BB10" t="n">
         <v>-0</v>
@@ -5716,16 +5716,16 @@
         <v>0</v>
       </c>
       <c r="BD10" t="n">
-        <v>0.0005742836117053927</v>
+        <v>-0.02982255625847399</v>
       </c>
       <c r="BE10" t="n">
         <v>0</v>
       </c>
       <c r="BF10" t="n">
-        <v>-0.05081621030623821</v>
+        <v>-0.08567962635708538</v>
       </c>
       <c r="BG10" t="n">
-        <v>-0.2254900379010922</v>
+        <v>-0.04018433983449842</v>
       </c>
       <c r="BH10" t="n">
         <v>0</v>
@@ -5734,34 +5734,34 @@
         <v>-0</v>
       </c>
       <c r="BJ10" t="n">
-        <v>0.001127989101185017</v>
+        <v>-0.03484821563854369</v>
       </c>
       <c r="BK10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BL10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BM10" t="n">
-        <v>0.1962072648876161</v>
+        <v>0.04867871491485575</v>
       </c>
       <c r="BN10" t="n">
         <v>-0</v>
       </c>
       <c r="BO10" t="n">
-        <v>0.1335026989040476</v>
+        <v>0.125339161417617</v>
       </c>
       <c r="BP10" t="n">
-        <v>0.1435319281603028</v>
+        <v>0.004210425681387839</v>
       </c>
       <c r="BQ10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BR10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BS10" t="n">
-        <v>0.035469156198079</v>
+        <v>0.0209953327982238</v>
       </c>
       <c r="BT10" t="n">
         <v>-0</v>
@@ -5770,43 +5770,43 @@
         <v>-0</v>
       </c>
       <c r="BV10" t="n">
-        <v>0.2843507423000579</v>
+        <v>0.2484806628937327</v>
       </c>
       <c r="BW10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BX10" t="n">
-        <v>0.03130934352958561</v>
+        <v>-0.1767606526204647</v>
       </c>
       <c r="BY10" t="n">
-        <v>0.04289298323694028</v>
+        <v>-0.1972974135040343</v>
       </c>
       <c r="BZ10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CA10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CB10" t="n">
-        <v>0.00716146867762661</v>
+        <v>-0.09772001080973249</v>
       </c>
       <c r="CC10" t="n">
         <v>-0</v>
       </c>
       <c r="CD10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CE10" t="n">
-        <v>-0.09010756691181397</v>
+        <v>-0.05293705197230539</v>
       </c>
       <c r="CF10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CG10" t="n">
-        <v>0.02491346119439617</v>
+        <v>0.1409998161326263</v>
       </c>
       <c r="CH10" t="n">
-        <v>-0.004180266447367667</v>
+        <v>0.05328413708466564</v>
       </c>
       <c r="CI10" t="n">
         <v>-0</v>
@@ -5815,52 +5815,52 @@
         <v>-0</v>
       </c>
       <c r="CK10" t="n">
-        <v>0.003244056717246182</v>
+        <v>-0.01999026794904066</v>
       </c>
       <c r="CL10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CM10" t="n">
         <v>0</v>
       </c>
       <c r="CN10" t="n">
-        <v>-0.1074216212221655</v>
+        <v>-0.01859529715628929</v>
       </c>
       <c r="CO10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CP10" t="n">
-        <v>-0.1387811405884853</v>
+        <v>0.1856867682714966</v>
       </c>
       <c r="CQ10" t="n">
-        <v>-0.03789243069636988</v>
+        <v>0.3081302365327517</v>
       </c>
       <c r="CR10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CS10" t="n">
         <v>-0</v>
       </c>
       <c r="CT10" t="n">
-        <v>0.06473816302205149</v>
+        <v>0.07574065725933965</v>
       </c>
       <c r="CU10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CV10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CW10" t="n">
-        <v>-0.05911811066190235</v>
+        <v>-0.05246379800144275</v>
       </c>
       <c r="CX10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CY10" t="n">
-        <v>0.05392983693807783</v>
+        <v>0.1631449086372251</v>
       </c>
       <c r="CZ10" t="n">
-        <v>0.001916941282543744</v>
+        <v>0.06926367112420254</v>
       </c>
       <c r="DA10" t="n">
         <v>0</v>
@@ -5869,52 +5869,52 @@
         <v>0</v>
       </c>
       <c r="DC10" t="n">
-        <v>0.003770140761499548</v>
+        <v>-0.00817545381039685</v>
       </c>
       <c r="DD10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DE10" t="n">
         <v>0</v>
       </c>
       <c r="DF10" t="n">
-        <v>-0.06619343505949368</v>
+        <v>-0.06230833165551228</v>
       </c>
       <c r="DG10" t="n">
         <v>0</v>
       </c>
       <c r="DH10" t="n">
-        <v>0.03864243271689098</v>
+        <v>0.06597271675517832</v>
       </c>
       <c r="DI10" t="n">
-        <v>0.0007765326439271461</v>
+        <v>-0.003739634223816181</v>
       </c>
       <c r="DJ10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DK10" t="n">
         <v>-0</v>
       </c>
       <c r="DL10" t="n">
-        <v>-0.001249753160966839</v>
+        <v>-0.03532082043843222</v>
       </c>
       <c r="DM10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DN10" t="n">
         <v>-0</v>
       </c>
       <c r="DO10" t="n">
-        <v>-0.09543144482651272</v>
+        <v>-0.05642211853092076</v>
       </c>
       <c r="DP10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DQ10" t="n">
-        <v>-0.03248281959398081</v>
+        <v>0.1187880338373385</v>
       </c>
       <c r="DR10" t="n">
-        <v>0.04093797765999912</v>
+        <v>-0.0598931028547426</v>
       </c>
       <c r="DS10" t="n">
         <v>-0</v>
@@ -5923,25 +5923,25 @@
         <v>-0</v>
       </c>
       <c r="DU10" t="n">
-        <v>-0.02854902207693516</v>
+        <v>0.1018984553933698</v>
       </c>
       <c r="DV10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DW10" t="n">
         <v>0</v>
       </c>
       <c r="DX10" t="n">
-        <v>-0.01859148393595788</v>
+        <v>0.0434472810988827</v>
       </c>
       <c r="DY10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DZ10" t="n">
-        <v>-0.0349405669881027</v>
+        <v>0.06667977239059113</v>
       </c>
       <c r="EA10" t="n">
-        <v>-0.05447151140479368</v>
+        <v>-0.1047452203856446</v>
       </c>
       <c r="EB10" t="n">
         <v>0</v>
@@ -5950,25 +5950,25 @@
         <v>-0</v>
       </c>
       <c r="ED10" t="n">
-        <v>-0.02399020796894651</v>
+        <v>0.09962917967669865</v>
       </c>
       <c r="EE10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EF10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EG10" t="n">
-        <v>-0.04170176355276701</v>
+        <v>0.03898912762783263</v>
       </c>
       <c r="EH10" t="n">
         <v>-0</v>
       </c>
       <c r="EI10" t="n">
-        <v>0.07249648662165721</v>
+        <v>0.08053081709046597</v>
       </c>
       <c r="EJ10" t="n">
-        <v>0.03902154001505594</v>
+        <v>0.03385119926832627</v>
       </c>
       <c r="EK10" t="n">
         <v>-0</v>
@@ -5977,79 +5977,79 @@
         <v>-0</v>
       </c>
       <c r="EM10" t="n">
-        <v>0.0386677947605337</v>
+        <v>-0.03749357158702035</v>
       </c>
       <c r="EN10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EO10" t="n">
         <v>0</v>
       </c>
       <c r="EP10" t="n">
-        <v>-0.1026925108799292</v>
+        <v>-0.03951860663764151</v>
       </c>
       <c r="EQ10" t="n">
         <v>-0</v>
       </c>
       <c r="ER10" t="n">
-        <v>0.1017130292855855</v>
+        <v>0.165349101305162</v>
       </c>
       <c r="ES10" t="n">
-        <v>-0.04193503589714117</v>
+        <v>-0.04270415668017147</v>
       </c>
       <c r="ET10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EU10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EV10" t="n">
-        <v>0.007514687907345938</v>
+        <v>0.02413612368648687</v>
       </c>
       <c r="EW10" t="n">
         <v>-0</v>
       </c>
       <c r="EX10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EY10" t="n">
-        <v>-0.0693353311579646</v>
+        <v>-0.07066564481234726</v>
       </c>
       <c r="EZ10" t="n">
         <v>-0</v>
       </c>
       <c r="FA10" t="n">
-        <v>0.04321543697571169</v>
+        <v>0.1807179434090647</v>
       </c>
       <c r="FB10" t="n">
-        <v>0.01877349442751917</v>
+        <v>0.06576648391298065</v>
       </c>
       <c r="FC10" t="n">
         <v>-0</v>
       </c>
       <c r="FD10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FE10" t="n">
-        <v>0.002156972398253379</v>
+        <v>-0.01085670414998314</v>
       </c>
       <c r="FF10" t="n">
         <v>-0</v>
       </c>
       <c r="FG10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FH10" t="n">
-        <v>0.06970085703452532</v>
+        <v>-0.01574145423874672</v>
       </c>
       <c r="FI10" t="n">
         <v>0</v>
       </c>
       <c r="FJ10" t="n">
-        <v>-0.04229933503048032</v>
+        <v>-0.01988018216471759</v>
       </c>
       <c r="FK10" t="n">
-        <v>-0.02874064022178571</v>
+        <v>0.0890830922361012</v>
       </c>
       <c r="FL10" t="n">
         <v>-0</v>
@@ -6058,25 +6058,25 @@
         <v>-0</v>
       </c>
       <c r="FN10" t="n">
-        <v>-0.002003899553037028</v>
+        <v>-0.05168310676274726</v>
       </c>
       <c r="FO10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FP10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FQ10" t="n">
-        <v>-0.1072047968446801</v>
+        <v>0.01274848251601898</v>
       </c>
       <c r="FR10" t="n">
         <v>0</v>
       </c>
       <c r="FS10" t="n">
-        <v>-0.06856727120654331</v>
+        <v>0.1331056439129447</v>
       </c>
       <c r="FT10" t="n">
-        <v>-0.0845509485773636</v>
+        <v>-0.1930717161047762</v>
       </c>
       <c r="FU10" t="n">
         <v>0</v>
@@ -6085,34 +6085,34 @@
         <v>0</v>
       </c>
       <c r="FW10" t="n">
-        <v>0.008923332559091156</v>
+        <v>-0.08579975124258682</v>
       </c>
       <c r="FX10" t="n">
         <v>0</v>
       </c>
       <c r="FY10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ10" t="n">
-        <v>-0.1103714945102075</v>
+        <v>-0.01045980617891625</v>
       </c>
       <c r="GA10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GB10" t="n">
-        <v>-0.03028872967025314</v>
+        <v>0.05714899770169404</v>
       </c>
       <c r="GC10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GD10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GE10" t="n">
         <v>-0</v>
       </c>
       <c r="GF10" t="n">
-        <v>0.02462169237773131</v>
+        <v>-0.05772176029605416</v>
       </c>
       <c r="GG10" t="n">
         <v>-0</v>
@@ -6120,28 +6120,28 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="B11" t="n">
-        <v>0.1569362592097218</v>
+        <v>0.3444080925396503</v>
       </c>
       <c r="C11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="D11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.09342170198541691</v>
+        <v>-0.01510938416056841</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.06869195636015804</v>
+        <v>-0.2023477065334461</v>
       </c>
       <c r="G11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="H11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="I11" t="n">
         <v>0</v>
@@ -6150,19 +6150,19 @@
         <v>0</v>
       </c>
       <c r="K11" t="n">
-        <v>0.08651367346981288</v>
+        <v>0.3817471402129924</v>
       </c>
       <c r="L11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="M11" t="n">
         <v>0</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.09032155982069168</v>
+        <v>-0.08206799041699429</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.05792321744204713</v>
+        <v>-0.145890543733612</v>
       </c>
       <c r="P11" t="n">
         <v>0</v>
@@ -6177,46 +6177,46 @@
         <v>-0</v>
       </c>
       <c r="T11" t="n">
-        <v>0.02508288174438282</v>
+        <v>0.07552640574773542</v>
       </c>
       <c r="U11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="V11" t="n">
         <v>0</v>
       </c>
       <c r="W11" t="n">
-        <v>0.005900850199492619</v>
+        <v>-0.07696544031106502</v>
       </c>
       <c r="X11" t="n">
-        <v>0.02722993912691613</v>
+        <v>0.01851703821092929</v>
       </c>
       <c r="Y11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AB11" t="n">
         <v>-0</v>
       </c>
       <c r="AC11" t="n">
-        <v>0.03811954005337733</v>
+        <v>-0.02824018016913161</v>
       </c>
       <c r="AD11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AE11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AF11" t="n">
-        <v>0.02163934130035201</v>
+        <v>-0.2447162922571671</v>
       </c>
       <c r="AG11" t="n">
-        <v>0.02309626613166187</v>
+        <v>0.0309748994190935</v>
       </c>
       <c r="AH11" t="n">
         <v>-0</v>
@@ -6231,7 +6231,7 @@
         <v>0</v>
       </c>
       <c r="AL11" t="n">
-        <v>0.02435113160945193</v>
+        <v>0.08061359008839071</v>
       </c>
       <c r="AM11" t="n">
         <v>0</v>
@@ -6240,13 +6240,13 @@
         <v>0</v>
       </c>
       <c r="AO11" t="n">
-        <v>-0.02155843525189223</v>
+        <v>-0.04918760272473718</v>
       </c>
       <c r="AP11" t="n">
-        <v>-0.01374384919679455</v>
+        <v>-0.03105924950051528</v>
       </c>
       <c r="AQ11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AR11" t="n">
         <v>-0</v>
@@ -6255,10 +6255,10 @@
         <v>0</v>
       </c>
       <c r="AT11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AU11" t="n">
-        <v>0.172927382276178</v>
+        <v>0.564156876595613</v>
       </c>
       <c r="AV11" t="n">
         <v>0</v>
@@ -6267,79 +6267,79 @@
         <v>0</v>
       </c>
       <c r="AX11" t="n">
-        <v>-0.01951744799238811</v>
+        <v>-0.2341303052332651</v>
       </c>
       <c r="AY11" t="n">
-        <v>-0.01274858253796787</v>
+        <v>-0.05315857069207077</v>
       </c>
       <c r="AZ11" t="n">
         <v>0</v>
       </c>
       <c r="BA11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BB11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BC11" t="n">
         <v>0</v>
       </c>
       <c r="BD11" t="n">
-        <v>0.03810078072694842</v>
+        <v>-0.04954338076924066</v>
       </c>
       <c r="BE11" t="n">
         <v>0</v>
       </c>
       <c r="BF11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BG11" t="n">
-        <v>-0.06819869623770639</v>
+        <v>-0.03114969812307425</v>
       </c>
       <c r="BH11" t="n">
-        <v>-0.0436386807748762</v>
+        <v>-0.08760408071697753</v>
       </c>
       <c r="BI11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BJ11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BK11" t="n">
         <v>0</v>
       </c>
       <c r="BL11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BM11" t="n">
-        <v>0.08811270720997005</v>
+        <v>0.1501979567188826</v>
       </c>
       <c r="BN11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BO11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BP11" t="n">
-        <v>0.05400506263256664</v>
+        <v>0.1499978593499852</v>
       </c>
       <c r="BQ11" t="n">
-        <v>0.02504682082886212</v>
+        <v>0.08701544179743526</v>
       </c>
       <c r="BR11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BS11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BT11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BU11" t="n">
         <v>-0</v>
       </c>
       <c r="BV11" t="n">
-        <v>0.07931069097314282</v>
+        <v>0.3694506605504524</v>
       </c>
       <c r="BW11" t="n">
         <v>0</v>
@@ -6348,43 +6348,43 @@
         <v>0</v>
       </c>
       <c r="BY11" t="n">
-        <v>-0.01114324072598321</v>
+        <v>-0.08280994451948327</v>
       </c>
       <c r="BZ11" t="n">
-        <v>0.02484462187655804</v>
+        <v>-0.04479441242172343</v>
       </c>
       <c r="CA11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CB11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CC11" t="n">
         <v>-0</v>
       </c>
       <c r="CD11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CE11" t="n">
-        <v>-0.03200783298663801</v>
+        <v>-0.1266573271483473</v>
       </c>
       <c r="CF11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CG11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CH11" t="n">
-        <v>0.0128733750645854</v>
+        <v>0.005047592027972926</v>
       </c>
       <c r="CI11" t="n">
-        <v>0.01578414727174791</v>
+        <v>0.07801846778490226</v>
       </c>
       <c r="CJ11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CK11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CL11" t="n">
         <v>-0</v>
@@ -6393,22 +6393,22 @@
         <v>0</v>
       </c>
       <c r="CN11" t="n">
-        <v>-0.0363846308764584</v>
+        <v>-0.2489927332408078</v>
       </c>
       <c r="CO11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CP11" t="n">
         <v>-0</v>
       </c>
       <c r="CQ11" t="n">
-        <v>-0.02389252520923997</v>
+        <v>0.08992290287244604</v>
       </c>
       <c r="CR11" t="n">
-        <v>-0.02416785270218321</v>
+        <v>0.01038948303687945</v>
       </c>
       <c r="CS11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CT11" t="n">
         <v>-0</v>
@@ -6417,28 +6417,28 @@
         <v>0</v>
       </c>
       <c r="CV11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CW11" t="n">
-        <v>-0.01734014163300348</v>
+        <v>-0.1087278799523171</v>
       </c>
       <c r="CX11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CY11" t="n">
         <v>0</v>
       </c>
       <c r="CZ11" t="n">
-        <v>0.01352014745087254</v>
+        <v>-0.01578579567840854</v>
       </c>
       <c r="DA11" t="n">
-        <v>0.01733753968688135</v>
+        <v>0.08056744635745905</v>
       </c>
       <c r="DB11" t="n">
         <v>0</v>
       </c>
       <c r="DC11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DD11" t="n">
         <v>0</v>
@@ -6447,7 +6447,7 @@
         <v>-0</v>
       </c>
       <c r="DF11" t="n">
-        <v>-0.04323560062037009</v>
+        <v>-0.09219693027017892</v>
       </c>
       <c r="DG11" t="n">
         <v>-0</v>
@@ -6456,37 +6456,37 @@
         <v>-0</v>
       </c>
       <c r="DI11" t="n">
-        <v>0.01232984833937633</v>
+        <v>-0.1490703459840717</v>
       </c>
       <c r="DJ11" t="n">
-        <v>0.003461258859911197</v>
+        <v>-0.005234865446636431</v>
       </c>
       <c r="DK11" t="n">
         <v>0</v>
       </c>
       <c r="DL11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DM11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DN11" t="n">
         <v>-0</v>
       </c>
       <c r="DO11" t="n">
-        <v>-0.03721735742702222</v>
+        <v>-0.07581191121905954</v>
       </c>
       <c r="DP11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DQ11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DR11" t="n">
-        <v>0.01329985542803208</v>
+        <v>-0.0360390833865476</v>
       </c>
       <c r="DS11" t="n">
-        <v>-0.0329157712729605</v>
+        <v>-0.01888707483693761</v>
       </c>
       <c r="DT11" t="n">
         <v>-0</v>
@@ -6501,7 +6501,7 @@
         <v>-0</v>
       </c>
       <c r="DX11" t="n">
-        <v>0.000578317813228914</v>
+        <v>0.07979814316197732</v>
       </c>
       <c r="DY11" t="n">
         <v>0</v>
@@ -6510,160 +6510,160 @@
         <v>-0</v>
       </c>
       <c r="EA11" t="n">
-        <v>-0.0375987599873849</v>
+        <v>0.005002911839944219</v>
       </c>
       <c r="EB11" t="n">
-        <v>-0.02221322630001556</v>
+        <v>0.05357608426633913</v>
       </c>
       <c r="EC11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ED11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EE11" t="n">
         <v>-0</v>
       </c>
       <c r="EF11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EG11" t="n">
-        <v>0.003097467469527432</v>
+        <v>0.0174789643509816</v>
       </c>
       <c r="EH11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EI11" t="n">
         <v>0</v>
       </c>
       <c r="EJ11" t="n">
-        <v>0.0134286539818204</v>
+        <v>-0.06217807248717567</v>
       </c>
       <c r="EK11" t="n">
-        <v>0.001557913730536646</v>
+        <v>0.06959931496366628</v>
       </c>
       <c r="EL11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EM11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EN11" t="n">
         <v>-0</v>
       </c>
       <c r="EO11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EP11" t="n">
-        <v>0.008218030888564336</v>
+        <v>0.001017621260907971</v>
       </c>
       <c r="EQ11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ER11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="ES11" t="n">
-        <v>0.002750377933215391</v>
+        <v>-0.1390825597430309</v>
       </c>
       <c r="ET11" t="n">
-        <v>0.02697807089695641</v>
+        <v>0.05346125432011329</v>
       </c>
       <c r="EU11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EV11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EW11" t="n">
         <v>0</v>
       </c>
       <c r="EX11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EY11" t="n">
-        <v>-0.01538292821171507</v>
+        <v>-0.1412102140830888</v>
       </c>
       <c r="EZ11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FA11" t="n">
         <v>-0</v>
       </c>
       <c r="FB11" t="n">
-        <v>0.01130176743160222</v>
+        <v>-0.03295945973026225</v>
       </c>
       <c r="FC11" t="n">
-        <v>0.02463457365433584</v>
+        <v>0.06019234849986711</v>
       </c>
       <c r="FD11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FE11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FF11" t="n">
         <v>-0</v>
       </c>
       <c r="FG11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FH11" t="n">
-        <v>-0.02093055021400882</v>
+        <v>-0.1289815880834328</v>
       </c>
       <c r="FI11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FJ11" t="n">
         <v>-0</v>
       </c>
       <c r="FK11" t="n">
-        <v>-0.0389365673472397</v>
+        <v>0.1536105446394784</v>
       </c>
       <c r="FL11" t="n">
-        <v>0.01852828987863536</v>
+        <v>0.02976575254683988</v>
       </c>
       <c r="FM11" t="n">
         <v>0</v>
       </c>
       <c r="FN11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FO11" t="n">
         <v>0</v>
       </c>
       <c r="FP11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FQ11" t="n">
-        <v>-0.0007203575416400899</v>
+        <v>0.07797410048268749</v>
       </c>
       <c r="FR11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FS11" t="n">
         <v>-0</v>
       </c>
       <c r="FT11" t="n">
-        <v>-0.01617177504096845</v>
+        <v>-0.1016708686614109</v>
       </c>
       <c r="FU11" t="n">
-        <v>0.01233379106609716</v>
+        <v>-0.01996804251716686</v>
       </c>
       <c r="FV11" t="n">
         <v>0</v>
       </c>
       <c r="FW11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FX11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FY11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ11" t="n">
-        <v>-0.05082967885549092</v>
+        <v>-0.07249149925584827</v>
       </c>
       <c r="GA11" t="n">
         <v>0</v>
@@ -6675,7 +6675,7 @@
         <v>-0</v>
       </c>
       <c r="GD11" t="n">
-        <v>-0.0215296435443643</v>
+        <v>0.08691499687612904</v>
       </c>
       <c r="GE11" t="n">
         <v>-0</v>
@@ -6692,22 +6692,22 @@
         <v>0</v>
       </c>
       <c r="B12" t="n">
-        <v>0.2138036718655256</v>
+        <v>0.361853728891756</v>
       </c>
       <c r="C12" t="n">
         <v>0</v>
       </c>
       <c r="D12" t="n">
-        <v>-0.1286896262190401</v>
+        <v>-0.1884042606045552</v>
       </c>
       <c r="E12" t="n">
-        <v>-0.002057982408033465</v>
+        <v>-0.01905891947417876</v>
       </c>
       <c r="F12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="G12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="H12" t="n">
         <v>-0</v>
@@ -6716,28 +6716,28 @@
         <v>0</v>
       </c>
       <c r="J12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K12" t="n">
-        <v>0.1225468372842711</v>
+        <v>0.3377599187861129</v>
       </c>
       <c r="L12" t="n">
         <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>-0.1077427978924793</v>
+        <v>-0.1852453197108808</v>
       </c>
       <c r="N12" t="n">
-        <v>-0.03144130433897796</v>
+        <v>-0.05389461279736659</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>
       </c>
       <c r="P12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Q12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="R12" t="n">
         <v>0</v>
@@ -6746,19 +6746,19 @@
         <v>0</v>
       </c>
       <c r="T12" t="n">
-        <v>0.0513467430628484</v>
+        <v>0.05755141655954076</v>
       </c>
       <c r="U12" t="n">
         <v>-0</v>
       </c>
       <c r="V12" t="n">
-        <v>0.01988408199003815</v>
+        <v>-0.02871143489311993</v>
       </c>
       <c r="W12" t="n">
-        <v>0.05120304080115017</v>
+        <v>-0.06352791405384293</v>
       </c>
       <c r="X12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Y12" t="n">
         <v>-0</v>
@@ -6770,79 +6770,79 @@
         <v>0</v>
       </c>
       <c r="AB12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AC12" t="n">
-        <v>0.1119828521842966</v>
+        <v>-0.08978075432540622</v>
       </c>
       <c r="AD12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AE12" t="n">
-        <v>-0.01569980060144378</v>
+        <v>-0.1077684485648951</v>
       </c>
       <c r="AF12" t="n">
-        <v>-0.01763455729446732</v>
+        <v>-0.07946441259363513</v>
       </c>
       <c r="AG12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AH12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AI12" t="n">
         <v>-0</v>
       </c>
       <c r="AJ12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AK12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AL12" t="n">
-        <v>0.002668509244190885</v>
+        <v>0.1017185135829084</v>
       </c>
       <c r="AM12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AN12" t="n">
-        <v>-0.02732235015468345</v>
+        <v>-0.08780425446760387</v>
       </c>
       <c r="AO12" t="n">
-        <v>-0.04973641960279803</v>
+        <v>0.04352014624252555</v>
       </c>
       <c r="AP12" t="n">
         <v>0</v>
       </c>
       <c r="AQ12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AR12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AS12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AT12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AU12" t="n">
-        <v>0.2984389787670303</v>
+        <v>0.2827175348223424</v>
       </c>
       <c r="AV12" t="n">
         <v>-0</v>
       </c>
       <c r="AW12" t="n">
-        <v>0.03294296170660795</v>
+        <v>-0.1232183976750381</v>
       </c>
       <c r="AX12" t="n">
-        <v>0.146079264126475</v>
+        <v>-0.1441930739069524</v>
       </c>
       <c r="AY12" t="n">
         <v>-0</v>
       </c>
       <c r="AZ12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BA12" t="n">
         <v>0</v>
@@ -6854,25 +6854,25 @@
         <v>0</v>
       </c>
       <c r="BD12" t="n">
-        <v>-0.01987641146363852</v>
+        <v>-0.002380856512826175</v>
       </c>
       <c r="BE12" t="n">
         <v>0</v>
       </c>
       <c r="BF12" t="n">
-        <v>-0.06450652496678494</v>
+        <v>-0.02188014419039118</v>
       </c>
       <c r="BG12" t="n">
-        <v>-0.0956634105843541</v>
+        <v>-0.01607973238120444</v>
       </c>
       <c r="BH12" t="n">
         <v>0</v>
       </c>
       <c r="BI12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BJ12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BK12" t="n">
         <v>0</v>
@@ -6881,22 +6881,22 @@
         <v>-0</v>
       </c>
       <c r="BM12" t="n">
-        <v>0.0869028548635173</v>
+        <v>-0.008686484523867697</v>
       </c>
       <c r="BN12" t="n">
         <v>-0</v>
       </c>
       <c r="BO12" t="n">
-        <v>0.01615972204122001</v>
+        <v>0.02705957916204954</v>
       </c>
       <c r="BP12" t="n">
-        <v>0.1065750069385509</v>
+        <v>0.06852924457480843</v>
       </c>
       <c r="BQ12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BR12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BS12" t="n">
         <v>-0</v>
@@ -6908,49 +6908,49 @@
         <v>-0</v>
       </c>
       <c r="BV12" t="n">
-        <v>0.156565191961594</v>
+        <v>0.2277121268237571</v>
       </c>
       <c r="BW12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BX12" t="n">
-        <v>0.0347272051863401</v>
+        <v>-0.1266170207992634</v>
       </c>
       <c r="BY12" t="n">
-        <v>0.08764612916983482</v>
+        <v>-0.04515175482719999</v>
       </c>
       <c r="BZ12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CA12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CB12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CC12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CD12" t="n">
         <v>-0</v>
       </c>
       <c r="CE12" t="n">
-        <v>-0.05104566000346365</v>
+        <v>-0.1175885951874398</v>
       </c>
       <c r="CF12" t="n">
         <v>-0</v>
       </c>
       <c r="CG12" t="n">
-        <v>-0.001451441499094302</v>
+        <v>0.117468738183352</v>
       </c>
       <c r="CH12" t="n">
-        <v>-0.01794605119685659</v>
+        <v>0.004516624564222434</v>
       </c>
       <c r="CI12" t="n">
         <v>0</v>
       </c>
       <c r="CJ12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CK12" t="n">
         <v>0</v>
@@ -6962,19 +6962,19 @@
         <v>0</v>
       </c>
       <c r="CN12" t="n">
-        <v>-0.04322564014717657</v>
+        <v>-0.05997712435206897</v>
       </c>
       <c r="CO12" t="n">
         <v>-0</v>
       </c>
       <c r="CP12" t="n">
-        <v>-0.1172093086663116</v>
+        <v>0.2291753062904144</v>
       </c>
       <c r="CQ12" t="n">
-        <v>-0.07106115182766486</v>
+        <v>0.03188364502778481</v>
       </c>
       <c r="CR12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CS12" t="n">
         <v>-0</v>
@@ -6989,25 +6989,25 @@
         <v>0</v>
       </c>
       <c r="CW12" t="n">
-        <v>-0.02271809144300696</v>
+        <v>-0.1093594612231825</v>
       </c>
       <c r="CX12" t="n">
         <v>0</v>
       </c>
       <c r="CY12" t="n">
-        <v>0.0122632056623175</v>
+        <v>0.1257727341932719</v>
       </c>
       <c r="CZ12" t="n">
-        <v>-0.01321078923932729</v>
+        <v>0.01116764483916112</v>
       </c>
       <c r="DA12" t="n">
         <v>-0</v>
       </c>
       <c r="DB12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DC12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DD12" t="n">
         <v>0</v>
@@ -7016,22 +7016,22 @@
         <v>0</v>
       </c>
       <c r="DF12" t="n">
-        <v>-0.0444464455426717</v>
+        <v>-0.08784756779818764</v>
       </c>
       <c r="DG12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DH12" t="n">
-        <v>0.01643427830483637</v>
+        <v>0.01393913334665172</v>
       </c>
       <c r="DI12" t="n">
-        <v>0.04570835480208914</v>
+        <v>-0.06570669027751981</v>
       </c>
       <c r="DJ12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DK12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DL12" t="n">
         <v>0</v>
@@ -7043,106 +7043,106 @@
         <v>-0</v>
       </c>
       <c r="DO12" t="n">
-        <v>-0.05877688782873926</v>
+        <v>-0.07822459281806018</v>
       </c>
       <c r="DP12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DQ12" t="n">
-        <v>0.01122447826428149</v>
+        <v>0.07137414760816531</v>
       </c>
       <c r="DR12" t="n">
-        <v>-0.03577036118512827</v>
+        <v>0.003754331113138715</v>
       </c>
       <c r="DS12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DT12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DU12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DV12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DW12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DX12" t="n">
-        <v>0.03634424683348283</v>
+        <v>0.03732115553687966</v>
       </c>
       <c r="DY12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DZ12" t="n">
-        <v>0.03727422090572064</v>
+        <v>-0.05256705739984068</v>
       </c>
       <c r="EA12" t="n">
-        <v>-0.006474602937477593</v>
+        <v>0.03177330818136916</v>
       </c>
       <c r="EB12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EC12" t="n">
         <v>-0</v>
       </c>
       <c r="ED12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EE12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EF12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EG12" t="n">
-        <v>-0.006211292057785087</v>
+        <v>-0.0625328119539038</v>
       </c>
       <c r="EH12" t="n">
         <v>-0</v>
       </c>
       <c r="EI12" t="n">
-        <v>0.04246775047128016</v>
+        <v>0.08868645224972189</v>
       </c>
       <c r="EJ12" t="n">
-        <v>0.04020158526480006</v>
+        <v>0.0351431888171711</v>
       </c>
       <c r="EK12" t="n">
         <v>0</v>
       </c>
       <c r="EL12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EM12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EN12" t="n">
         <v>-0</v>
       </c>
       <c r="EO12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EP12" t="n">
-        <v>-0.03358797073576396</v>
+        <v>-0.04634244471165452</v>
       </c>
       <c r="EQ12" t="n">
         <v>-0</v>
       </c>
       <c r="ER12" t="n">
-        <v>0.01801872524090663</v>
+        <v>0.06433854224916463</v>
       </c>
       <c r="ES12" t="n">
-        <v>0.04654649642982299</v>
+        <v>-0.03891342374045356</v>
       </c>
       <c r="ET12" t="n">
         <v>-0</v>
       </c>
       <c r="EU12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EV12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EW12" t="n">
         <v>-0</v>
@@ -7151,22 +7151,22 @@
         <v>-0</v>
       </c>
       <c r="EY12" t="n">
-        <v>-0.03539540260610522</v>
+        <v>-0.1231549849593862</v>
       </c>
       <c r="EZ12" t="n">
         <v>-0</v>
       </c>
       <c r="FA12" t="n">
-        <v>0.005505948377040618</v>
+        <v>0.1362535417499208</v>
       </c>
       <c r="FB12" t="n">
-        <v>0.001310321779417219</v>
+        <v>-0.011238959336101</v>
       </c>
       <c r="FC12" t="n">
         <v>-0</v>
       </c>
       <c r="FD12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FE12" t="n">
         <v>0</v>
@@ -7175,19 +7175,19 @@
         <v>-0</v>
       </c>
       <c r="FG12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FH12" t="n">
-        <v>0.04146629580049153</v>
+        <v>-0.07796277257528815</v>
       </c>
       <c r="FI12" t="n">
         <v>-0</v>
       </c>
       <c r="FJ12" t="n">
-        <v>0.01013644736558332</v>
+        <v>0.07388388232269973</v>
       </c>
       <c r="FK12" t="n">
-        <v>-0.03483748511447808</v>
+        <v>-0.0006497258833100794</v>
       </c>
       <c r="FL12" t="n">
         <v>-0</v>
@@ -7196,28 +7196,28 @@
         <v>0</v>
       </c>
       <c r="FN12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FO12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FP12" t="n">
         <v>-0</v>
       </c>
       <c r="FQ12" t="n">
-        <v>-0.04671656746486463</v>
+        <v>-0.0217197998263739</v>
       </c>
       <c r="FR12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FS12" t="n">
-        <v>-0.05049342417167667</v>
+        <v>0.1305713646041761</v>
       </c>
       <c r="FT12" t="n">
-        <v>0.07090434998427896</v>
+        <v>-0.02907609220672144</v>
       </c>
       <c r="FU12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FV12" t="n">
         <v>-0</v>
@@ -7226,34 +7226,34 @@
         <v>0</v>
       </c>
       <c r="FX12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FY12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ12" t="n">
-        <v>-0.0008026344451012347</v>
+        <v>-0.09656858166132318</v>
       </c>
       <c r="GA12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GB12" t="n">
-        <v>-0.07695442769525436</v>
+        <v>0.07042645275822988</v>
       </c>
       <c r="GC12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GD12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GE12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GF12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GG12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13">
@@ -7261,19 +7261,19 @@
         <v>0</v>
       </c>
       <c r="B13" t="n">
-        <v>0.430849711078083</v>
+        <v>0.4131720183116147</v>
       </c>
       <c r="C13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="D13" t="n">
         <v>0</v>
       </c>
       <c r="E13" t="n">
-        <v>-0.1125953887861414</v>
+        <v>0.04827671460218361</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.3580518666320245</v>
+        <v>-0.3524539568940934</v>
       </c>
       <c r="G13" t="n">
         <v>0</v>
@@ -7285,28 +7285,28 @@
         <v>0</v>
       </c>
       <c r="J13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="K13" t="n">
-        <v>0.2932753883524122</v>
+        <v>0.5214585148316295</v>
       </c>
       <c r="L13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="M13" t="n">
         <v>0</v>
       </c>
       <c r="N13" t="n">
-        <v>-0.09557268034411515</v>
+        <v>-0.03242016659166709</v>
       </c>
       <c r="O13" t="n">
-        <v>-0.3195760440783538</v>
+        <v>-0.3221847492095702</v>
       </c>
       <c r="P13" t="n">
         <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="R13" t="n">
         <v>0</v>
@@ -7315,25 +7315,25 @@
         <v>-0</v>
       </c>
       <c r="T13" t="n">
-        <v>0.07121113052928069</v>
+        <v>0.1660431163004108</v>
       </c>
       <c r="U13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="V13" t="n">
         <v>0</v>
       </c>
       <c r="W13" t="n">
-        <v>0.003679998988713432</v>
+        <v>-0.218546840656286</v>
       </c>
       <c r="X13" t="n">
-        <v>0.00186740508096706</v>
+        <v>-0.03994041210090308</v>
       </c>
       <c r="Y13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA13" t="n">
         <v>0</v>
@@ -7342,19 +7342,19 @@
         <v>-0</v>
       </c>
       <c r="AC13" t="n">
-        <v>0.06848331763772682</v>
+        <v>-0.05226416027928005</v>
       </c>
       <c r="AD13" t="n">
         <v>0</v>
       </c>
       <c r="AE13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AF13" t="n">
-        <v>0.06187622827565622</v>
+        <v>-0.4276085982634453</v>
       </c>
       <c r="AG13" t="n">
-        <v>-0.02711373983213619</v>
+        <v>-0.2443598450260613</v>
       </c>
       <c r="AH13" t="n">
         <v>-0</v>
@@ -7369,7 +7369,7 @@
         <v>0</v>
       </c>
       <c r="AL13" t="n">
-        <v>0.05736332063742373</v>
+        <v>0.09907392065032783</v>
       </c>
       <c r="AM13" t="n">
         <v>0</v>
@@ -7378,13 +7378,13 @@
         <v>0</v>
       </c>
       <c r="AO13" t="n">
-        <v>-0.0007993764432883022</v>
+        <v>-0.004505399927558187</v>
       </c>
       <c r="AP13" t="n">
-        <v>-0.05650242950569442</v>
+        <v>-0.1526478620233861</v>
       </c>
       <c r="AQ13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AR13" t="n">
         <v>-0</v>
@@ -7393,10 +7393,10 @@
         <v>0</v>
       </c>
       <c r="AT13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AU13" t="n">
-        <v>0.3853141527392022</v>
+        <v>0.9036703003176463</v>
       </c>
       <c r="AV13" t="n">
         <v>-0</v>
@@ -7405,67 +7405,67 @@
         <v>0</v>
       </c>
       <c r="AX13" t="n">
-        <v>-0.01293364107327167</v>
+        <v>-0.2006238412939215</v>
       </c>
       <c r="AY13" t="n">
-        <v>-0.1628490539884914</v>
+        <v>-0.180293505438825</v>
       </c>
       <c r="AZ13" t="n">
         <v>0</v>
       </c>
       <c r="BA13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BB13" t="n">
         <v>0</v>
       </c>
       <c r="BC13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BD13" t="n">
-        <v>0.1019805834308209</v>
+        <v>-0.1569722798131201</v>
       </c>
       <c r="BE13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BF13" t="n">
         <v>0</v>
       </c>
       <c r="BG13" t="n">
-        <v>-0.1123582518531781</v>
+        <v>-0.1599389067526316</v>
       </c>
       <c r="BH13" t="n">
-        <v>-0.1310031826060753</v>
+        <v>-0.1953760333526879</v>
       </c>
       <c r="BI13" t="n">
         <v>0</v>
       </c>
       <c r="BJ13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BK13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BL13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BM13" t="n">
-        <v>0.1397572689088138</v>
+        <v>0.1171508701517925</v>
       </c>
       <c r="BN13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BO13" t="n">
         <v>-0</v>
       </c>
       <c r="BP13" t="n">
-        <v>0.07909213563993564</v>
+        <v>0.1182542492209019</v>
       </c>
       <c r="BQ13" t="n">
-        <v>0.03157458772772736</v>
+        <v>-0.00519934513644466</v>
       </c>
       <c r="BR13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BS13" t="n">
         <v>0</v>
@@ -7474,76 +7474,76 @@
         <v>-0</v>
       </c>
       <c r="BU13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BV13" t="n">
-        <v>0.1974885995558234</v>
+        <v>0.4733295255260652</v>
       </c>
       <c r="BW13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BX13" t="n">
         <v>0</v>
       </c>
       <c r="BY13" t="n">
-        <v>-0.04854590373497503</v>
+        <v>-0.2041751886476508</v>
       </c>
       <c r="BZ13" t="n">
-        <v>-0.1020312245006874</v>
+        <v>-0.2765829221715372</v>
       </c>
       <c r="CA13" t="n">
         <v>-0</v>
       </c>
       <c r="CB13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CC13" t="n">
         <v>0</v>
       </c>
       <c r="CD13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CE13" t="n">
-        <v>-0.08789813662988362</v>
+        <v>-0.1669603685634686</v>
       </c>
       <c r="CF13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CG13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CH13" t="n">
-        <v>-0.009278629321913022</v>
+        <v>0.05518002462558203</v>
       </c>
       <c r="CI13" t="n">
-        <v>0.0833704200091137</v>
+        <v>0.1525195055217523</v>
       </c>
       <c r="CJ13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CK13" t="n">
         <v>0</v>
       </c>
       <c r="CL13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CM13" t="n">
         <v>0</v>
       </c>
       <c r="CN13" t="n">
-        <v>-0.08682575255297417</v>
+        <v>-0.4265514035698776</v>
       </c>
       <c r="CO13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CP13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CQ13" t="n">
-        <v>-0.0387372151334556</v>
+        <v>0.4856391112598771</v>
       </c>
       <c r="CR13" t="n">
-        <v>-0.004697561838289501</v>
+        <v>0.3663181789728243</v>
       </c>
       <c r="CS13" t="n">
         <v>-0</v>
@@ -7558,22 +7558,22 @@
         <v>-0</v>
       </c>
       <c r="CW13" t="n">
-        <v>-0.06234064556811734</v>
+        <v>-0.1516697332412926</v>
       </c>
       <c r="CX13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CY13" t="n">
         <v>0</v>
       </c>
       <c r="CZ13" t="n">
-        <v>-0.004193390005516712</v>
+        <v>0.02230974019313456</v>
       </c>
       <c r="DA13" t="n">
-        <v>0.08713655792591443</v>
+        <v>0.1221407659780385</v>
       </c>
       <c r="DB13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DC13" t="n">
         <v>-0</v>
@@ -7582,25 +7582,25 @@
         <v>0</v>
       </c>
       <c r="DE13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DF13" t="n">
-        <v>-0.07673744461063975</v>
+        <v>0.008355066057957805</v>
       </c>
       <c r="DG13" t="n">
         <v>0</v>
       </c>
       <c r="DH13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DI13" t="n">
-        <v>0.01307561481185642</v>
+        <v>-0.1597202068846816</v>
       </c>
       <c r="DJ13" t="n">
-        <v>0.01079765937860536</v>
+        <v>0.001581850305665502</v>
       </c>
       <c r="DK13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DL13" t="n">
         <v>0</v>
@@ -7609,28 +7609,28 @@
         <v>0</v>
       </c>
       <c r="DN13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DO13" t="n">
-        <v>-0.05510708878457855</v>
+        <v>0.01544233300732095</v>
       </c>
       <c r="DP13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DQ13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DR13" t="n">
-        <v>0.02083822932615374</v>
+        <v>0.0221380457735142</v>
       </c>
       <c r="DS13" t="n">
-        <v>0.003424230112236681</v>
+        <v>0.08862166931799735</v>
       </c>
       <c r="DT13" t="n">
         <v>-0</v>
       </c>
       <c r="DU13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DV13" t="n">
         <v>0</v>
@@ -7639,22 +7639,22 @@
         <v>-0</v>
       </c>
       <c r="DX13" t="n">
-        <v>0.01425882029001314</v>
+        <v>0.1164163578956304</v>
       </c>
       <c r="DY13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DZ13" t="n">
         <v>-0</v>
       </c>
       <c r="EA13" t="n">
-        <v>0.0002172061994789206</v>
+        <v>-0.04552206621545411</v>
       </c>
       <c r="EB13" t="n">
-        <v>0.01565892277139339</v>
+        <v>0.0765274841718934</v>
       </c>
       <c r="EC13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ED13" t="n">
         <v>-0</v>
@@ -7666,34 +7666,34 @@
         <v>0</v>
       </c>
       <c r="EG13" t="n">
-        <v>-0.02607467512241916</v>
+        <v>-0.05593255104790983</v>
       </c>
       <c r="EH13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EI13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EJ13" t="n">
-        <v>0.01858677401302842</v>
+        <v>-0.05429173297930177</v>
       </c>
       <c r="EK13" t="n">
-        <v>0.07743588098738552</v>
+        <v>-0.000378487168223561</v>
       </c>
       <c r="EL13" t="n">
         <v>-0</v>
       </c>
       <c r="EM13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EN13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EO13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EP13" t="n">
-        <v>-0.00814839216461585</v>
+        <v>-0.02560332146166972</v>
       </c>
       <c r="EQ13" t="n">
         <v>0</v>
@@ -7702,13 +7702,13 @@
         <v>-0</v>
       </c>
       <c r="ES13" t="n">
-        <v>-0.01549018364994561</v>
+        <v>-0.03990743380039135</v>
       </c>
       <c r="ET13" t="n">
-        <v>0.07841993013797342</v>
+        <v>0.133428427254798</v>
       </c>
       <c r="EU13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EV13" t="n">
         <v>0</v>
@@ -7717,55 +7717,55 @@
         <v>-0</v>
       </c>
       <c r="EX13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EY13" t="n">
-        <v>-0.05842819958474935</v>
+        <v>-0.1884806429072524</v>
       </c>
       <c r="EZ13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FA13" t="n">
         <v>-0</v>
       </c>
       <c r="FB13" t="n">
-        <v>-0.003458306950172684</v>
+        <v>0.005290289115789111</v>
       </c>
       <c r="FC13" t="n">
-        <v>0.08802578724961771</v>
+        <v>0.1313443654988471</v>
       </c>
       <c r="FD13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FE13" t="n">
         <v>0</v>
       </c>
       <c r="FF13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FG13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FH13" t="n">
-        <v>-0.05116534314782933</v>
+        <v>-0.196636405851926</v>
       </c>
       <c r="FI13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FJ13" t="n">
         <v>-0</v>
       </c>
       <c r="FK13" t="n">
-        <v>-0.009560220010617786</v>
+        <v>0.07803603974520541</v>
       </c>
       <c r="FL13" t="n">
-        <v>-0.06173559237342281</v>
+        <v>-0.07256243611527266</v>
       </c>
       <c r="FM13" t="n">
         <v>0</v>
       </c>
       <c r="FN13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FO13" t="n">
         <v>0</v>
@@ -7774,19 +7774,19 @@
         <v>0</v>
       </c>
       <c r="FQ13" t="n">
-        <v>0.01178988409834254</v>
+        <v>0.07453243329167139</v>
       </c>
       <c r="FR13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FS13" t="n">
         <v>-0</v>
       </c>
       <c r="FT13" t="n">
-        <v>-0.05591824607964548</v>
+        <v>0.1118129596745633</v>
       </c>
       <c r="FU13" t="n">
-        <v>-0.00983351546061462</v>
+        <v>-0.0293862002945841</v>
       </c>
       <c r="FV13" t="n">
         <v>-0</v>
@@ -7795,25 +7795,25 @@
         <v>0</v>
       </c>
       <c r="FX13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FY13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ13" t="n">
-        <v>-0.04084723151766995</v>
+        <v>-0.05288430745233148</v>
       </c>
       <c r="GA13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GB13" t="n">
         <v>-0</v>
       </c>
       <c r="GC13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GD13" t="n">
-        <v>-0.04145461507212536</v>
+        <v>0.05490863638400185</v>
       </c>
       <c r="GE13" t="n">
         <v>-0</v>
@@ -7822,7 +7822,7 @@
         <v>-0</v>
       </c>
       <c r="GG13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14">
@@ -7830,43 +7830,43 @@
         <v>0</v>
       </c>
       <c r="B14" t="n">
-        <v>0.4157210176042634</v>
+        <v>0.3927087962994225</v>
       </c>
       <c r="C14" t="n">
         <v>0</v>
       </c>
       <c r="D14" t="n">
-        <v>-0.1130988769271953</v>
+        <v>-0.2350329460858874</v>
       </c>
       <c r="E14" t="n">
-        <v>-0.1057554808657881</v>
+        <v>-0.04219069501937853</v>
       </c>
       <c r="F14" t="n">
         <v>0</v>
       </c>
       <c r="G14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="H14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="I14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="K14" t="n">
-        <v>0.2414726929450312</v>
+        <v>0.3470255785868724</v>
       </c>
       <c r="L14" t="n">
         <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>-0.08368847291174865</v>
+        <v>-0.2424067089879495</v>
       </c>
       <c r="N14" t="n">
-        <v>-0.08250836963132144</v>
+        <v>-0.1271472286835166</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
@@ -7881,73 +7881,73 @@
         <v>0</v>
       </c>
       <c r="S14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="T14" t="n">
-        <v>0.08997718278185202</v>
+        <v>0.05317062420968576</v>
       </c>
       <c r="U14" t="n">
         <v>-0</v>
       </c>
       <c r="V14" t="n">
-        <v>-0.01290317106585711</v>
+        <v>-0.04689252241021043</v>
       </c>
       <c r="W14" t="n">
-        <v>0.04893398094642282</v>
+        <v>-0.05275044882289237</v>
       </c>
       <c r="X14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Y14" t="n">
         <v>-0</v>
       </c>
       <c r="Z14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA14" t="n">
         <v>0</v>
       </c>
       <c r="AB14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AC14" t="n">
-        <v>0.06228462848484698</v>
+        <v>-0.01101030383398707</v>
       </c>
       <c r="AD14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AE14" t="n">
-        <v>0.006855969156761295</v>
+        <v>-0.220153678338304</v>
       </c>
       <c r="AF14" t="n">
-        <v>0.0002772424476278649</v>
+        <v>-0.1451035497328116</v>
       </c>
       <c r="AG14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AH14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AI14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AJ14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AK14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AL14" t="n">
-        <v>-0.002003098674274765</v>
+        <v>0.1556818568529964</v>
       </c>
       <c r="AM14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AN14" t="n">
-        <v>-0.05341283119981638</v>
+        <v>-0.1000683577944079</v>
       </c>
       <c r="AO14" t="n">
-        <v>-0.06056906645482067</v>
+        <v>0.07162782169560636</v>
       </c>
       <c r="AP14" t="n">
         <v>0</v>
@@ -7962,28 +7962,28 @@
         <v>0</v>
       </c>
       <c r="AT14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AU14" t="n">
-        <v>0.3449192007995648</v>
+        <v>0.4200337522792271</v>
       </c>
       <c r="AV14" t="n">
         <v>-0</v>
       </c>
       <c r="AW14" t="n">
-        <v>0.05279588681199725</v>
+        <v>-0.0674987489630418</v>
       </c>
       <c r="AX14" t="n">
-        <v>0.05935435820238882</v>
+        <v>-0.3125337044123455</v>
       </c>
       <c r="AY14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AZ14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BA14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BB14" t="n">
         <v>-0</v>
@@ -7992,49 +7992,49 @@
         <v>0</v>
       </c>
       <c r="BD14" t="n">
-        <v>0.02622525915449221</v>
+        <v>-0.009968449195645088</v>
       </c>
       <c r="BE14" t="n">
         <v>0</v>
       </c>
       <c r="BF14" t="n">
-        <v>-0.07040594002936269</v>
+        <v>-0.05256811915801666</v>
       </c>
       <c r="BG14" t="n">
-        <v>-0.1403950435006977</v>
+        <v>0.08952519207388725</v>
       </c>
       <c r="BH14" t="n">
         <v>0</v>
       </c>
       <c r="BI14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BJ14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BK14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BL14" t="n">
         <v>-0</v>
       </c>
       <c r="BM14" t="n">
-        <v>0.0906621654572856</v>
+        <v>0.07506938316909505</v>
       </c>
       <c r="BN14" t="n">
         <v>-0</v>
       </c>
       <c r="BO14" t="n">
-        <v>0.04184942593336886</v>
+        <v>0.02112298927599302</v>
       </c>
       <c r="BP14" t="n">
-        <v>0.1185537001299674</v>
+        <v>0.116328721384283</v>
       </c>
       <c r="BQ14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BR14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BS14" t="n">
         <v>-0</v>
@@ -8043,46 +8043,46 @@
         <v>-0</v>
       </c>
       <c r="BU14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BV14" t="n">
-        <v>0.1604292119649297</v>
+        <v>0.3164933561190191</v>
       </c>
       <c r="BW14" t="n">
         <v>0</v>
       </c>
       <c r="BX14" t="n">
-        <v>0.05916795058510288</v>
+        <v>-0.1552626525069434</v>
       </c>
       <c r="BY14" t="n">
-        <v>0.0324390624577246</v>
+        <v>-0.06248433795701323</v>
       </c>
       <c r="BZ14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CA14" t="n">
         <v>-0</v>
       </c>
       <c r="CB14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CC14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CD14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CE14" t="n">
-        <v>-0.09063581083931237</v>
+        <v>-0.1415206283203914</v>
       </c>
       <c r="CF14" t="n">
         <v>-0</v>
       </c>
       <c r="CG14" t="n">
-        <v>0.006328798117189445</v>
+        <v>0.1220197113556596</v>
       </c>
       <c r="CH14" t="n">
-        <v>-0.01080489537107809</v>
+        <v>0.05164862161576109</v>
       </c>
       <c r="CI14" t="n">
         <v>0</v>
@@ -8100,46 +8100,46 @@
         <v>0</v>
       </c>
       <c r="CN14" t="n">
-        <v>-0.008737115160389258</v>
+        <v>-0.2572284779415429</v>
       </c>
       <c r="CO14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CP14" t="n">
-        <v>-0.08224758892108287</v>
+        <v>0.3070074784137234</v>
       </c>
       <c r="CQ14" t="n">
-        <v>-0.07718373546034976</v>
+        <v>0.07082801530705096</v>
       </c>
       <c r="CR14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CS14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CT14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CU14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CV14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CW14" t="n">
-        <v>-0.07195422441351954</v>
+        <v>-0.1251149772287775</v>
       </c>
       <c r="CX14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CY14" t="n">
-        <v>0.02197820565162761</v>
+        <v>0.144662031625159</v>
       </c>
       <c r="CZ14" t="n">
-        <v>-0.01088173560147142</v>
+        <v>0.05108083744875137</v>
       </c>
       <c r="DA14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DB14" t="n">
         <v>0</v>
@@ -8154,22 +8154,22 @@
         <v>0</v>
       </c>
       <c r="DF14" t="n">
-        <v>0.002632410690297865</v>
+        <v>0.00279911468618785</v>
       </c>
       <c r="DG14" t="n">
         <v>0</v>
       </c>
       <c r="DH14" t="n">
-        <v>0.01800537975880481</v>
+        <v>0.01271853031899386</v>
       </c>
       <c r="DI14" t="n">
-        <v>0.04032296825232287</v>
+        <v>-0.06540725800345019</v>
       </c>
       <c r="DJ14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DK14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DL14" t="n">
         <v>0</v>
@@ -8181,43 +8181,43 @@
         <v>-0</v>
       </c>
       <c r="DO14" t="n">
-        <v>-0.04567194507043751</v>
+        <v>-0.1559958363243441</v>
       </c>
       <c r="DP14" t="n">
         <v>0</v>
       </c>
       <c r="DQ14" t="n">
-        <v>0.06057254055034241</v>
+        <v>-0.06580331485584917</v>
       </c>
       <c r="DR14" t="n">
-        <v>-0.04832170853164212</v>
+        <v>0.04461010676872099</v>
       </c>
       <c r="DS14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DT14" t="n">
         <v>-0</v>
       </c>
       <c r="DU14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DV14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DW14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DX14" t="n">
-        <v>0.02803243819833417</v>
+        <v>0.09658791261065591</v>
       </c>
       <c r="DY14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DZ14" t="n">
-        <v>-0.002360018974442748</v>
+        <v>0.06222960813071781</v>
       </c>
       <c r="EA14" t="n">
-        <v>-0.08195473438457566</v>
+        <v>-0.1453653881893715</v>
       </c>
       <c r="EB14" t="n">
         <v>0</v>
@@ -8229,22 +8229,22 @@
         <v>0</v>
       </c>
       <c r="EE14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EF14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EG14" t="n">
-        <v>-0.08940104990286528</v>
+        <v>-0.01991997876523053</v>
       </c>
       <c r="EH14" t="n">
         <v>-0</v>
       </c>
       <c r="EI14" t="n">
-        <v>0.02634265590553355</v>
+        <v>0.0800147123098167</v>
       </c>
       <c r="EJ14" t="n">
-        <v>0.06460343493227505</v>
+        <v>0.08012691342039359</v>
       </c>
       <c r="EK14" t="n">
         <v>0</v>
@@ -8262,97 +8262,97 @@
         <v>0</v>
       </c>
       <c r="EP14" t="n">
-        <v>-0.03702591341140891</v>
+        <v>-0.08576808810284066</v>
       </c>
       <c r="EQ14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ER14" t="n">
-        <v>0.02548358369606507</v>
+        <v>0.1195728139195182</v>
       </c>
       <c r="ES14" t="n">
-        <v>0.005287369178860078</v>
+        <v>-0.05598517742749964</v>
       </c>
       <c r="ET14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EU14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EV14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EW14" t="n">
         <v>-0</v>
       </c>
       <c r="EX14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EY14" t="n">
-        <v>-0.07153567408493937</v>
+        <v>-0.1483488052655236</v>
       </c>
       <c r="EZ14" t="n">
         <v>-0</v>
       </c>
       <c r="FA14" t="n">
-        <v>0.01270604370247221</v>
+        <v>0.1540133640849587</v>
       </c>
       <c r="FB14" t="n">
-        <v>0.008749485326731444</v>
+        <v>0.03039974862217844</v>
       </c>
       <c r="FC14" t="n">
         <v>-0</v>
       </c>
       <c r="FD14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FE14" t="n">
         <v>0</v>
       </c>
       <c r="FF14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FG14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FH14" t="n">
-        <v>0.001890884390385129</v>
+        <v>0.004116218370370113</v>
       </c>
       <c r="FI14" t="n">
         <v>-0</v>
       </c>
       <c r="FJ14" t="n">
-        <v>0.05141749248313847</v>
+        <v>0.03881717077560338</v>
       </c>
       <c r="FK14" t="n">
-        <v>-0.07210178696452106</v>
+        <v>-0.09867638779515187</v>
       </c>
       <c r="FL14" t="n">
         <v>-0</v>
       </c>
       <c r="FM14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FN14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FO14" t="n">
         <v>0</v>
       </c>
       <c r="FP14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FQ14" t="n">
-        <v>-0.005090512335192129</v>
+        <v>-0.00173571965452162</v>
       </c>
       <c r="FR14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FS14" t="n">
-        <v>0.009223029162050552</v>
+        <v>0.06299374247164878</v>
       </c>
       <c r="FT14" t="n">
-        <v>-0.006652912864971066</v>
+        <v>-0.05753959309391879</v>
       </c>
       <c r="FU14" t="n">
         <v>-0</v>
@@ -8361,7 +8361,7 @@
         <v>0</v>
       </c>
       <c r="FW14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FX14" t="n">
         <v>0</v>
@@ -8370,22 +8370,22 @@
         <v>-0</v>
       </c>
       <c r="FZ14" t="n">
-        <v>0.001669471045212574</v>
+        <v>-0.09181770767872553</v>
       </c>
       <c r="GA14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GB14" t="n">
-        <v>-0.06147142513062498</v>
+        <v>0.1047146098280079</v>
       </c>
       <c r="GC14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GD14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GE14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GF14" t="n">
         <v>0</v>
@@ -8399,25 +8399,25 @@
         <v>-0</v>
       </c>
       <c r="B15" t="n">
-        <v>-0.5256608714867217</v>
+        <v>-0.7151835339121291</v>
       </c>
       <c r="C15" t="n">
         <v>-0</v>
       </c>
       <c r="D15" t="n">
-        <v>0.2372601573803971</v>
+        <v>0.242355638029512</v>
       </c>
       <c r="E15" t="n">
-        <v>0.1264791430087394</v>
+        <v>0.2034626496373257</v>
       </c>
       <c r="F15" t="n">
         <v>-0</v>
       </c>
       <c r="G15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="H15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="I15" t="n">
         <v>-0</v>
@@ -8426,43 +8426,43 @@
         <v>-0</v>
       </c>
       <c r="K15" t="n">
-        <v>-0.3803576293280561</v>
+        <v>-0.6000408676881172</v>
       </c>
       <c r="L15" t="n">
         <v>-0</v>
       </c>
       <c r="M15" t="n">
-        <v>0.2763327806832541</v>
+        <v>0.4240870372388411</v>
       </c>
       <c r="N15" t="n">
-        <v>0.08088713317604285</v>
+        <v>0.2880596897855332</v>
       </c>
       <c r="O15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="P15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="R15" t="n">
         <v>-0</v>
       </c>
       <c r="S15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.1158435947994318</v>
+        <v>-0.08417552039033659</v>
       </c>
       <c r="U15" t="n">
         <v>0</v>
       </c>
       <c r="V15" t="n">
-        <v>0.03680415494114984</v>
+        <v>0.07638401002285097</v>
       </c>
       <c r="W15" t="n">
-        <v>-0.03446470561912136</v>
+        <v>-0.05873119889161157</v>
       </c>
       <c r="X15" t="n">
         <v>0</v>
@@ -8477,55 +8477,55 @@
         <v>-0</v>
       </c>
       <c r="AB15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AC15" t="n">
-        <v>-0.1876990535294692</v>
+        <v>-0.05095381115583011</v>
       </c>
       <c r="AD15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AE15" t="n">
-        <v>0.01170688824847394</v>
+        <v>0.2363331547904576</v>
       </c>
       <c r="AF15" t="n">
-        <v>0.007586976533853781</v>
+        <v>0.0637532916550905</v>
       </c>
       <c r="AG15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AH15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AI15" t="n">
         <v>0</v>
       </c>
       <c r="AJ15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AK15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AL15" t="n">
-        <v>-0.04928140101838897</v>
+        <v>-0.2830308164041561</v>
       </c>
       <c r="AM15" t="n">
         <v>-0</v>
       </c>
       <c r="AN15" t="n">
-        <v>0.03818859760764937</v>
+        <v>0.06400879029974745</v>
       </c>
       <c r="AO15" t="n">
-        <v>0.02031856285163157</v>
+        <v>-0.2489990878202357</v>
       </c>
       <c r="AP15" t="n">
         <v>-0</v>
       </c>
       <c r="AQ15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AR15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AS15" t="n">
         <v>-0</v>
@@ -8534,19 +8534,19 @@
         <v>0</v>
       </c>
       <c r="AU15" t="n">
-        <v>-0.3256480142850736</v>
+        <v>-0.5548023421917534</v>
       </c>
       <c r="AV15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AW15" t="n">
-        <v>-0.05474512345080687</v>
+        <v>0.1224730688247332</v>
       </c>
       <c r="AX15" t="n">
-        <v>-0.02059746135874782</v>
+        <v>0.1153299474404897</v>
       </c>
       <c r="AY15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AZ15" t="n">
         <v>0</v>
@@ -8561,16 +8561,16 @@
         <v>-0</v>
       </c>
       <c r="BD15" t="n">
-        <v>-0.07945504439882344</v>
+        <v>0.05179978135750658</v>
       </c>
       <c r="BE15" t="n">
         <v>-0</v>
       </c>
       <c r="BF15" t="n">
-        <v>0.1328397053119369</v>
+        <v>0.1155472318173679</v>
       </c>
       <c r="BG15" t="n">
-        <v>0.333688786875114</v>
+        <v>0.259546344267201</v>
       </c>
       <c r="BH15" t="n">
         <v>-0</v>
@@ -8579,7 +8579,7 @@
         <v>-0</v>
       </c>
       <c r="BJ15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BK15" t="n">
         <v>-0</v>
@@ -8588,43 +8588,43 @@
         <v>0</v>
       </c>
       <c r="BM15" t="n">
-        <v>-0.01659478363990655</v>
+        <v>0.07802123819067601</v>
       </c>
       <c r="BN15" t="n">
         <v>0</v>
       </c>
       <c r="BO15" t="n">
-        <v>-0.0562459185160734</v>
+        <v>0.03102106131177631</v>
       </c>
       <c r="BP15" t="n">
-        <v>0.03538356896376418</v>
+        <v>0.0124421959255727</v>
       </c>
       <c r="BQ15" t="n">
         <v>0</v>
       </c>
       <c r="BR15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BS15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BT15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BU15" t="n">
         <v>0</v>
       </c>
       <c r="BV15" t="n">
-        <v>-0.2087422137719682</v>
+        <v>-0.464523478983156</v>
       </c>
       <c r="BW15" t="n">
         <v>-0</v>
       </c>
       <c r="BX15" t="n">
-        <v>0.07674390091418885</v>
+        <v>0.098474520883107</v>
       </c>
       <c r="BY15" t="n">
-        <v>-0.05659921742681904</v>
+        <v>-0.02253062496416598</v>
       </c>
       <c r="BZ15" t="n">
         <v>-0</v>
@@ -8633,7 +8633,7 @@
         <v>0</v>
       </c>
       <c r="CB15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CC15" t="n">
         <v>-0</v>
@@ -8642,46 +8642,46 @@
         <v>0</v>
       </c>
       <c r="CE15" t="n">
-        <v>0.1165939957277442</v>
+        <v>0.2931256749609315</v>
       </c>
       <c r="CF15" t="n">
         <v>0</v>
       </c>
       <c r="CG15" t="n">
-        <v>-0.03583001618079656</v>
+        <v>-0.06363731537587582</v>
       </c>
       <c r="CH15" t="n">
-        <v>0.05939541001859362</v>
+        <v>-0.03468267512809772</v>
       </c>
       <c r="CI15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CJ15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CK15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CL15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CM15" t="n">
         <v>-0</v>
       </c>
       <c r="CN15" t="n">
-        <v>-0.01952781767632982</v>
+        <v>0.2991939649918595</v>
       </c>
       <c r="CO15" t="n">
         <v>0</v>
       </c>
       <c r="CP15" t="n">
-        <v>0.001572994314786233</v>
+        <v>-0.1265598648883828</v>
       </c>
       <c r="CQ15" t="n">
-        <v>0.03210437482526948</v>
+        <v>-0.2966899695204772</v>
       </c>
       <c r="CR15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CS15" t="n">
         <v>0</v>
@@ -8696,70 +8696,70 @@
         <v>-0</v>
       </c>
       <c r="CW15" t="n">
-        <v>0.115058760694598</v>
+        <v>0.2884104716203941</v>
       </c>
       <c r="CX15" t="n">
         <v>-0</v>
       </c>
       <c r="CY15" t="n">
-        <v>-0.04635080060702636</v>
+        <v>-0.08837201413151205</v>
       </c>
       <c r="CZ15" t="n">
-        <v>0.03745151959759679</v>
+        <v>-0.05252372370345633</v>
       </c>
       <c r="DA15" t="n">
         <v>-0</v>
       </c>
       <c r="DB15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DC15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DD15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DE15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DF15" t="n">
-        <v>0.1040313050979296</v>
+        <v>0.04430657356607069</v>
       </c>
       <c r="DG15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DH15" t="n">
-        <v>-0.03055475562145342</v>
+        <v>-0.01340609069943624</v>
       </c>
       <c r="DI15" t="n">
-        <v>-0.0001664196873230549</v>
+        <v>-0.003794516338682064</v>
       </c>
       <c r="DJ15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DK15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DL15" t="n">
         <v>-0</v>
       </c>
       <c r="DM15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DN15" t="n">
         <v>0</v>
       </c>
       <c r="DO15" t="n">
-        <v>0.102869935105254</v>
+        <v>0.18529340434275</v>
       </c>
       <c r="DP15" t="n">
         <v>0</v>
       </c>
       <c r="DQ15" t="n">
-        <v>-0.06807450256638709</v>
+        <v>0.001545651913897873</v>
       </c>
       <c r="DR15" t="n">
-        <v>0.1388539752554495</v>
+        <v>-0.005521913296855557</v>
       </c>
       <c r="DS15" t="n">
         <v>-0</v>
@@ -8774,22 +8774,22 @@
         <v>-0</v>
       </c>
       <c r="DW15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DX15" t="n">
-        <v>-0.0480228718327592</v>
+        <v>0.02715854495870827</v>
       </c>
       <c r="DY15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DZ15" t="n">
-        <v>0.12404410306456</v>
+        <v>0.004438291484639938</v>
       </c>
       <c r="EA15" t="n">
-        <v>-0.08580580587989037</v>
+        <v>-0.03478517871580063</v>
       </c>
       <c r="EB15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EC15" t="n">
         <v>0</v>
@@ -8804,25 +8804,25 @@
         <v>0</v>
       </c>
       <c r="EG15" t="n">
-        <v>0.06644936454427376</v>
+        <v>0.2833411117631858</v>
       </c>
       <c r="EH15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EI15" t="n">
-        <v>-0.02959208326944606</v>
+        <v>-0.04280778615380121</v>
       </c>
       <c r="EJ15" t="n">
-        <v>-0.05857540766975586</v>
+        <v>-0.008185375651946923</v>
       </c>
       <c r="EK15" t="n">
         <v>0</v>
       </c>
       <c r="EL15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EM15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EN15" t="n">
         <v>-0</v>
@@ -8831,70 +8831,70 @@
         <v>-0</v>
       </c>
       <c r="EP15" t="n">
-        <v>0.08505892253252721</v>
+        <v>0.2367113479541108</v>
       </c>
       <c r="EQ15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ER15" t="n">
-        <v>0.07263912253869399</v>
+        <v>-0.09423214370192132</v>
       </c>
       <c r="ES15" t="n">
-        <v>-0.07654455944747302</v>
+        <v>-0.1280766705115065</v>
       </c>
       <c r="ET15" t="n">
         <v>0</v>
       </c>
       <c r="EU15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EV15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EW15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EX15" t="n">
         <v>0</v>
       </c>
       <c r="EY15" t="n">
-        <v>0.1365094691416994</v>
+        <v>0.3487877693155053</v>
       </c>
       <c r="EZ15" t="n">
         <v>0</v>
       </c>
       <c r="FA15" t="n">
-        <v>-0.06368706610830124</v>
+        <v>-0.0673340484624417</v>
       </c>
       <c r="FB15" t="n">
-        <v>0.03120721329800244</v>
+        <v>-0.04068354426782964</v>
       </c>
       <c r="FC15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FD15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FE15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FF15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FG15" t="n">
         <v>0</v>
       </c>
       <c r="FH15" t="n">
-        <v>0.04120657910296781</v>
+        <v>0.1674473785698843</v>
       </c>
       <c r="FI15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FJ15" t="n">
-        <v>-0.05801382895367035</v>
+        <v>-0.08662265833492612</v>
       </c>
       <c r="FK15" t="n">
-        <v>0.02541160581604044</v>
+        <v>0.02795577819839217</v>
       </c>
       <c r="FL15" t="n">
         <v>0</v>
@@ -8906,90 +8906,90 @@
         <v>-0</v>
       </c>
       <c r="FO15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FP15" t="n">
         <v>0</v>
       </c>
       <c r="FQ15" t="n">
-        <v>0.01373754752597957</v>
+        <v>0.02958361123625471</v>
       </c>
       <c r="FR15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FS15" t="n">
-        <v>0.1175451917420798</v>
+        <v>-0.221650121919663</v>
       </c>
       <c r="FT15" t="n">
-        <v>-0.03024280881182445</v>
+        <v>-0.01137616090786598</v>
       </c>
       <c r="FU15" t="n">
         <v>0</v>
       </c>
       <c r="FV15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FW15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FX15" t="n">
         <v>-0</v>
       </c>
       <c r="FY15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FZ15" t="n">
-        <v>0.07400739902756229</v>
+        <v>0.1540597710598433</v>
       </c>
       <c r="GA15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GB15" t="n">
-        <v>0.119139845877772</v>
+        <v>0.06177489101543931</v>
       </c>
       <c r="GC15" t="n">
         <v>-0</v>
       </c>
       <c r="GD15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GE15" t="n">
         <v>0</v>
       </c>
       <c r="GF15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GG15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="B16" t="n">
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>0.345198972699999</v>
+        <v>0.3918224337637696</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.1149010954060778</v>
+        <v>-0.17807659983618</v>
       </c>
       <c r="E16" t="n">
-        <v>-0.05145191441207728</v>
+        <v>0.2021202796045098</v>
       </c>
       <c r="F16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="G16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="H16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="I16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="J16" t="n">
         <v>-0</v>
@@ -8998,22 +8998,22 @@
         <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>0.2903394076540288</v>
+        <v>0.3912405614407177</v>
       </c>
       <c r="M16" t="n">
-        <v>-0.09754515767015579</v>
+        <v>-0.140318667444475</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.1250989370770266</v>
+        <v>0.07612529463127318</v>
       </c>
       <c r="O16" t="n">
         <v>0</v>
       </c>
       <c r="P16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
         <v>0</v>
@@ -9025,22 +9025,22 @@
         <v>0</v>
       </c>
       <c r="U16" t="n">
-        <v>0.0957173463036691</v>
+        <v>0.07615831375928968</v>
       </c>
       <c r="V16" t="n">
-        <v>-0.0391264290245921</v>
+        <v>-0.1133212494800851</v>
       </c>
       <c r="W16" t="n">
-        <v>0.02383538232412771</v>
+        <v>-0.07000106024959576</v>
       </c>
       <c r="X16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Y16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA16" t="n">
         <v>-0</v>
@@ -9049,16 +9049,16 @@
         <v>-0</v>
       </c>
       <c r="AC16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AD16" t="n">
-        <v>0.0488924213904005</v>
+        <v>0.06737717910512243</v>
       </c>
       <c r="AE16" t="n">
-        <v>0.03350293848373585</v>
+        <v>0.1224224568069991</v>
       </c>
       <c r="AF16" t="n">
-        <v>0.05859225640272011</v>
+        <v>0.05796365123774398</v>
       </c>
       <c r="AG16" t="n">
         <v>0</v>
@@ -9067,61 +9067,61 @@
         <v>-0</v>
       </c>
       <c r="AI16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AJ16" t="n">
         <v>0</v>
       </c>
       <c r="AK16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AL16" t="n">
         <v>0</v>
       </c>
       <c r="AM16" t="n">
-        <v>-0.0213908436052626</v>
+        <v>0.1278377070940931</v>
       </c>
       <c r="AN16" t="n">
-        <v>-0.03515697874399307</v>
+        <v>-0.094469766120523</v>
       </c>
       <c r="AO16" t="n">
-        <v>-0.07720740554791077</v>
+        <v>-0.06341202618382066</v>
       </c>
       <c r="AP16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AQ16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AR16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AS16" t="n">
         <v>-0</v>
       </c>
       <c r="AT16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AU16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AV16" t="n">
-        <v>0.1511335665700965</v>
+        <v>0.3677789336671797</v>
       </c>
       <c r="AW16" t="n">
-        <v>-0.03737031061207872</v>
+        <v>-0.3431221135133382</v>
       </c>
       <c r="AX16" t="n">
-        <v>0.1622124129109514</v>
+        <v>0.0461368330452008</v>
       </c>
       <c r="AY16" t="n">
         <v>-0</v>
       </c>
       <c r="AZ16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BA16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BB16" t="n">
         <v>-0</v>
@@ -9130,16 +9130,16 @@
         <v>-0</v>
       </c>
       <c r="BD16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BE16" t="n">
-        <v>0.07763924246271658</v>
+        <v>-0.002314133620633777</v>
       </c>
       <c r="BF16" t="n">
-        <v>-0.02503407220329837</v>
+        <v>0.1473414271404999</v>
       </c>
       <c r="BG16" t="n">
-        <v>-0.0866652026136296</v>
+        <v>0.1151599706551402</v>
       </c>
       <c r="BH16" t="n">
         <v>0</v>
@@ -9154,19 +9154,19 @@
         <v>0</v>
       </c>
       <c r="BL16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BM16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BN16" t="n">
-        <v>0.05200513554166711</v>
+        <v>-0.04400079616917262</v>
       </c>
       <c r="BO16" t="n">
-        <v>0.05404558318025639</v>
+        <v>-0.09347266351788681</v>
       </c>
       <c r="BP16" t="n">
-        <v>0.1345479166322357</v>
+        <v>-0.1495200751674317</v>
       </c>
       <c r="BQ16" t="n">
         <v>-0</v>
@@ -9178,25 +9178,25 @@
         <v>0</v>
       </c>
       <c r="BT16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BU16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BV16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BW16" t="n">
-        <v>0.05803994295864351</v>
+        <v>0.2429273160155317</v>
       </c>
       <c r="BX16" t="n">
-        <v>-0.05141999250373239</v>
+        <v>-0.3708205206974164</v>
       </c>
       <c r="BY16" t="n">
-        <v>0.109955437929343</v>
+        <v>-0.008071734384140335</v>
       </c>
       <c r="BZ16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CA16" t="n">
         <v>0</v>
@@ -9211,43 +9211,43 @@
         <v>-0</v>
       </c>
       <c r="CE16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CF16" t="n">
-        <v>-0.06736061492964805</v>
+        <v>-0.1246240210564133</v>
       </c>
       <c r="CG16" t="n">
-        <v>0.03317236837575027</v>
+        <v>0.07040555714291254</v>
       </c>
       <c r="CH16" t="n">
-        <v>-0.002252753124409441</v>
+        <v>-0.01098659873521368</v>
       </c>
       <c r="CI16" t="n">
         <v>0</v>
       </c>
       <c r="CJ16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CK16" t="n">
         <v>0</v>
       </c>
       <c r="CL16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CM16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CN16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CO16" t="n">
-        <v>0.02459010693545122</v>
+        <v>-0.1351745158455313</v>
       </c>
       <c r="CP16" t="n">
-        <v>-0.008768544958123074</v>
+        <v>0.09626292178162714</v>
       </c>
       <c r="CQ16" t="n">
-        <v>-0.1103037781817533</v>
+        <v>0.05095914005420213</v>
       </c>
       <c r="CR16" t="n">
         <v>0</v>
@@ -9268,40 +9268,40 @@
         <v>0</v>
       </c>
       <c r="CX16" t="n">
-        <v>-0.04929794135728201</v>
+        <v>-0.09414514324197785</v>
       </c>
       <c r="CY16" t="n">
-        <v>0.0332406161621606</v>
+        <v>0.06706928082062218</v>
       </c>
       <c r="CZ16" t="n">
-        <v>0.0224914196120334</v>
+        <v>-0.03266820081470014</v>
       </c>
       <c r="DA16" t="n">
         <v>-0</v>
       </c>
       <c r="DB16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DC16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DD16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DE16" t="n">
         <v>-0</v>
       </c>
       <c r="DF16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DG16" t="n">
-        <v>-0.03470942551622853</v>
+        <v>-0.02498569492917342</v>
       </c>
       <c r="DH16" t="n">
-        <v>0.0431176308505376</v>
+        <v>0.04506738346430225</v>
       </c>
       <c r="DI16" t="n">
-        <v>-0.004948437272397194</v>
+        <v>-0.01252353059065757</v>
       </c>
       <c r="DJ16" t="n">
         <v>0</v>
@@ -9313,49 +9313,49 @@
         <v>0</v>
       </c>
       <c r="DM16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DN16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DO16" t="n">
         <v>-0</v>
       </c>
       <c r="DP16" t="n">
-        <v>0.009870477526400049</v>
+        <v>-0.0107123034085641</v>
       </c>
       <c r="DQ16" t="n">
-        <v>0.03490516087646607</v>
+        <v>0.05250379421628584</v>
       </c>
       <c r="DR16" t="n">
-        <v>-0.153689748957685</v>
+        <v>-0.08466186239593983</v>
       </c>
       <c r="DS16" t="n">
         <v>-0</v>
       </c>
       <c r="DT16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DU16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DV16" t="n">
         <v>0</v>
       </c>
       <c r="DW16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DX16" t="n">
         <v>0</v>
       </c>
       <c r="DY16" t="n">
-        <v>0.06141528719383687</v>
+        <v>-0.01087254131254949</v>
       </c>
       <c r="DZ16" t="n">
-        <v>-0.01450880171458373</v>
+        <v>0.02264014503570957</v>
       </c>
       <c r="EA16" t="n">
-        <v>-0.07155596274381316</v>
+        <v>0.07435813208258604</v>
       </c>
       <c r="EB16" t="n">
         <v>0</v>
@@ -9364,106 +9364,106 @@
         <v>-0</v>
       </c>
       <c r="ED16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EE16" t="n">
         <v>-0</v>
       </c>
       <c r="EF16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EG16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EH16" t="n">
-        <v>-0.1118637068464601</v>
+        <v>-0.03570084611628428</v>
       </c>
       <c r="EI16" t="n">
-        <v>0.05134876090173277</v>
+        <v>0.03381620338953943</v>
       </c>
       <c r="EJ16" t="n">
-        <v>0.06382787617717829</v>
+        <v>0.05006126521156325</v>
       </c>
       <c r="EK16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EL16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EM16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EN16" t="n">
         <v>-0</v>
       </c>
       <c r="EO16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EP16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EQ16" t="n">
-        <v>-0.01184996076442923</v>
+        <v>-0.08058166646215642</v>
       </c>
       <c r="ER16" t="n">
-        <v>0.02475890972432485</v>
+        <v>0.09956683593845818</v>
       </c>
       <c r="ES16" t="n">
-        <v>0.02373722596379775</v>
+        <v>-0.003475533513910612</v>
       </c>
       <c r="ET16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EU16" t="n">
         <v>0</v>
       </c>
       <c r="EV16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EW16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EX16" t="n">
         <v>-0</v>
       </c>
       <c r="EY16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EZ16" t="n">
-        <v>-0.06185639127134192</v>
+        <v>-0.1155178085178967</v>
       </c>
       <c r="FA16" t="n">
-        <v>0.04668949649203157</v>
+        <v>0.1065147585936588</v>
       </c>
       <c r="FB16" t="n">
-        <v>0.02180987576796098</v>
+        <v>-0.01696551009429648</v>
       </c>
       <c r="FC16" t="n">
         <v>0</v>
       </c>
       <c r="FD16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FE16" t="n">
         <v>0</v>
       </c>
       <c r="FF16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FG16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FH16" t="n">
         <v>-0</v>
       </c>
       <c r="FI16" t="n">
-        <v>-0.006755249434751366</v>
+        <v>-0.1534102811926409</v>
       </c>
       <c r="FJ16" t="n">
-        <v>0.001999001047889296</v>
+        <v>0.05620980329431698</v>
       </c>
       <c r="FK16" t="n">
-        <v>0.06858414679854917</v>
+        <v>0.0855335004085888</v>
       </c>
       <c r="FL16" t="n">
         <v>-0</v>
@@ -9472,7 +9472,7 @@
         <v>0</v>
       </c>
       <c r="FN16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FO16" t="n">
         <v>0</v>
@@ -9481,40 +9481,40 @@
         <v>-0</v>
       </c>
       <c r="FQ16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FR16" t="n">
-        <v>-0.003782882669082777</v>
+        <v>-0.006406957325280878</v>
       </c>
       <c r="FS16" t="n">
-        <v>-0.006776623877901009</v>
+        <v>-0.004333879191704597</v>
       </c>
       <c r="FT16" t="n">
-        <v>0.0513294444931864</v>
+        <v>0.05763689898176726</v>
       </c>
       <c r="FU16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FV16" t="n">
         <v>-0</v>
       </c>
       <c r="FW16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FX16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FY16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GA16" t="n">
-        <v>0.04385569555685608</v>
+        <v>-0.008030433858293816</v>
       </c>
       <c r="GB16" t="n">
-        <v>-0.04488804793894059</v>
+        <v>0.1523782083691178</v>
       </c>
       <c r="GC16" t="n">
         <v>-0</v>
@@ -9526,10 +9526,10 @@
         <v>-0</v>
       </c>
       <c r="GF16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GG16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
     </row>
   </sheetData>
